--- a/LG_Handles_Titles.xlsx
+++ b/LG_Handles_Titles.xlsx
@@ -31,7 +31,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -48,11 +48,6 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -66,12 +61,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -9377,86 +9371,98 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="4" t="inlineStr">
+      <c r="A280" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/agm73329015</t>
         </is>
       </c>
-      <c r="B280" s="4" t="inlineStr">
+      <c r="B280" t="inlineStr">
         <is>
           <t>agm73329015</t>
         </is>
       </c>
-      <c r="C280" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D280" s="4" t="inlineStr"/>
-      <c r="E280" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F280" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>LG Range Touch Control Panel Assembly - AGM73329015</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>lgparts.com (range collection), walmart.com</t>
         </is>
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="4" t="inlineStr">
+      <c r="A281" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/adc76265705</t>
         </is>
       </c>
-      <c r="B281" s="4" t="inlineStr">
+      <c r="B281" s="3" t="inlineStr">
         <is>
           <t>adc76265705</t>
         </is>
       </c>
-      <c r="C281" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D281" s="4" t="inlineStr"/>
-      <c r="E281" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F281" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C281" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D281" s="3" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Door Assembly - ADC76265705</t>
+        </is>
+      </c>
+      <c r="E281" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F281" s="3" t="inlineStr">
+        <is>
+          <t>exact number not found; siblings ADC74265705 (refrigerator door assy) and ADC76265716 (home bar door assy) on lgparts.com</t>
         </is>
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="4" t="inlineStr">
+      <c r="A282" s="2" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/5075ja1029s</t>
         </is>
       </c>
-      <c r="B282" s="4" t="inlineStr">
+      <c r="B282" s="2" t="inlineStr">
         <is>
           <t>5075ja1029s</t>
         </is>
       </c>
-      <c r="C282" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D282" s="4" t="inlineStr"/>
-      <c r="E282" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F282" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C282" s="2" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Ice Bucket Assembly - 5075JA1029S</t>
+        </is>
+      </c>
+      <c r="E282" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F282" s="2" t="inlineStr">
+        <is>
+          <t>exact number not found; siblings 5075JA1029J/5075JA1029Y are ice bucket assemblies on lgparts.com</t>
         </is>
       </c>
     </row>
@@ -9653,86 +9659,98 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="4" t="inlineStr">
+      <c r="A289" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/akb74375403</t>
         </is>
       </c>
-      <c r="B289" s="4" t="inlineStr">
+      <c r="B289" t="inlineStr">
         <is>
           <t>akb74375403</t>
         </is>
       </c>
-      <c r="C289" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D289" s="4" t="inlineStr"/>
-      <c r="E289" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F289" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>LG Air Conditioner Remote Control - AKB74375403</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>lgparts.com titled Air Conditioner Remote Control; ricambi.com.au</t>
         </is>
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="4" t="inlineStr">
+      <c r="A290" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/ebr85194760</t>
         </is>
       </c>
-      <c r="B290" s="4" t="inlineStr">
+      <c r="B290" s="3" t="inlineStr">
         <is>
           <t>ebr85194760</t>
         </is>
       </c>
-      <c r="C290" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D290" s="4" t="inlineStr"/>
-      <c r="E290" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F290" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C290" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D290" s="3" t="inlineStr">
+        <is>
+          <t>LG Washer Display PCB Assembly - EBR85194760</t>
+        </is>
+      </c>
+      <c r="E290" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F290" s="3" t="inlineStr">
+        <is>
+          <t>exact number not found; siblings EBR85194721/EBR85194705 are washer display PCBs (lgparts.com, shopjimmy.com)</t>
         </is>
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="4" t="inlineStr">
+      <c r="A291" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/aeq36756912</t>
         </is>
       </c>
-      <c r="B291" s="4" t="inlineStr">
+      <c r="B291" t="inlineStr">
         <is>
           <t>aeq36756912</t>
         </is>
       </c>
-      <c r="C291" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D291" s="4" t="inlineStr"/>
-      <c r="E291" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F291" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Ice Maker Assembly Kit - AEQ36756912</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>lgparts.com, appliancepartspros.com; discontinued; replaces AEQ36756914/AEQ36756926</t>
         </is>
       </c>
     </row>
@@ -9769,30 +9787,34 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="4" t="inlineStr">
+      <c r="A293" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/afg73629708</t>
         </is>
       </c>
-      <c r="B293" s="4" t="inlineStr">
+      <c r="B293" t="inlineStr">
         <is>
           <t>afg73629708</t>
         </is>
       </c>
-      <c r="C293" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D293" s="4" t="inlineStr"/>
-      <c r="E293" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F293" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>LG Washer Lid Assembly - AFG73629708</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>lgparts.com titled Washer Lid</t>
         </is>
       </c>
     </row>
@@ -9893,58 +9915,66 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="4" t="inlineStr">
+      <c r="A297" s="2" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/adx75550610</t>
         </is>
       </c>
-      <c r="B297" s="4" t="inlineStr">
+      <c r="B297" s="2" t="inlineStr">
         <is>
           <t>adx75550610</t>
         </is>
       </c>
-      <c r="C297" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D297" s="4" t="inlineStr"/>
-      <c r="E297" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F297" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C297" s="2" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D297" s="2" t="inlineStr">
+        <is>
+          <t>LG Washer Door Gasket Assembly - ADX75550610</t>
+        </is>
+      </c>
+      <c r="E297" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F297" s="2" t="inlineStr">
+        <is>
+          <t>lgparts.com lists Gasket Assembly, Door; appliance inferred (front-load washer gasket); ADX75550601 discontinued sibling</t>
         </is>
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="4" t="inlineStr">
+      <c r="A298" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/3581ja8814b</t>
         </is>
       </c>
-      <c r="B298" s="4" t="inlineStr">
+      <c r="B298" t="inlineStr">
         <is>
           <t>3581ja8814b</t>
         </is>
       </c>
-      <c r="C298" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D298" s="4" t="inlineStr"/>
-      <c r="E298" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F298" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Door Assembly - 3581JA8814B</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>lgparts.com (refrigerator door assembly)</t>
         </is>
       </c>
     </row>
@@ -10045,30 +10075,34 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="4" t="inlineStr">
+      <c r="A302" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/mhy62644404</t>
         </is>
       </c>
-      <c r="B302" s="4" t="inlineStr">
+      <c r="B302" s="3" t="inlineStr">
         <is>
           <t>mhy62644404</t>
         </is>
       </c>
-      <c r="C302" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D302" s="4" t="inlineStr"/>
-      <c r="E302" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F302" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C302" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D302" s="3" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Hinge Spring - MHY62644404</t>
+        </is>
+      </c>
+      <c r="E302" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F302" s="3" t="inlineStr">
+        <is>
+          <t>exact number not found; siblings MHY62644402 spring (walmart), MHY62644804 hinge spring (lgparts); appliance guessed</t>
         </is>
       </c>
     </row>
@@ -10169,30 +10203,34 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="4" t="inlineStr">
+      <c r="A306" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/5209el1002f</t>
         </is>
       </c>
-      <c r="B306" s="4" t="inlineStr">
+      <c r="B306" t="inlineStr">
         <is>
           <t>5209el1002f</t>
         </is>
       </c>
-      <c r="C306" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D306" s="4" t="inlineStr"/>
-      <c r="E306" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F306" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>LG Dryer Duct Assembly - 5209EL1002F</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>lgparts.com dryer-parts collection; appliancefactoryparts.com fits washer-dryer combos WKEX200HBA etc.</t>
         </is>
       </c>
     </row>
@@ -10229,30 +10267,34 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="4" t="inlineStr">
+      <c r="A308" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/ebr86692722</t>
         </is>
       </c>
-      <c r="B308" s="4" t="inlineStr">
+      <c r="B308" t="inlineStr">
         <is>
           <t>ebr86692722</t>
         </is>
       </c>
-      <c r="C308" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D308" s="4" t="inlineStr"/>
-      <c r="E308" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F308" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>LG Washer Main Control Board - EBR86692722</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>lgparts.com, ebay.com (fits WT7305CW)</t>
         </is>
       </c>
     </row>
@@ -10289,30 +10331,34 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="4" t="inlineStr">
+      <c r="A310" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/aaa74310305</t>
         </is>
       </c>
-      <c r="B310" s="4" t="inlineStr">
+      <c r="B310" t="inlineStr">
         <is>
           <t>aaa74310305</t>
         </is>
       </c>
-      <c r="C310" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D310" s="4" t="inlineStr"/>
-      <c r="E310" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F310" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>LG Sound Bar Speaker Accessory Assembly - AAA74310305</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>lgparts.com titled Sound Bar Speaker Accessory Assembly</t>
         </is>
       </c>
     </row>
@@ -10349,30 +10395,34 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="4" t="inlineStr">
+      <c r="A312" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/4026er4004b</t>
         </is>
       </c>
-      <c r="B312" s="4" t="inlineStr">
+      <c r="B312" t="inlineStr">
         <is>
           <t>4026er4004b</t>
         </is>
       </c>
-      <c r="C312" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D312" s="4" t="inlineStr"/>
-      <c r="E312" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F312" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>LG Washer Door Hook Locker - 4026ER4004B</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>lgparts.com LG Washer Hook Locker; washer-dryer models</t>
         </is>
       </c>
     </row>
@@ -10441,30 +10491,34 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="4" t="inlineStr">
+      <c r="A315" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/acv72909506</t>
         </is>
       </c>
-      <c r="B315" s="4" t="inlineStr">
+      <c r="B315" t="inlineStr">
         <is>
           <t>acv72909506</t>
         </is>
       </c>
-      <c r="C315" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D315" s="4" t="inlineStr"/>
-      <c r="E315" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F315" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>LG Washer Friction Damper - ACV72909506</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>lgparts.com, ebay; superseded by ACV72909503 per filtersfast.com</t>
         </is>
       </c>
     </row>
@@ -10565,114 +10619,130 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="4" t="inlineStr">
+      <c r="A319" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/aan76430636</t>
         </is>
       </c>
-      <c r="B319" s="4" t="inlineStr">
+      <c r="B319" s="3" t="inlineStr">
         <is>
           <t>aan76430636</t>
         </is>
       </c>
-      <c r="C319" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D319" s="4" t="inlineStr"/>
-      <c r="E319" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F319" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C319" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D319" s="3" t="inlineStr">
+        <is>
+          <t>LG Television Stand Base Assembly - AAN76430636</t>
+        </is>
+      </c>
+      <c r="E319" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F319" s="3" t="inlineStr">
+        <is>
+          <t>exact not found; siblings AAN76430613/18/10/06 base assembly (lgparts, repairclinic); TV inferred from AAN base prefix</t>
         </is>
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="4" t="inlineStr">
+      <c r="A320" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/ebr42923402</t>
         </is>
       </c>
-      <c r="B320" s="4" t="inlineStr">
+      <c r="B320" t="inlineStr">
         <is>
           <t>ebr42923402</t>
         </is>
       </c>
-      <c r="C320" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D320" s="4" t="inlineStr"/>
-      <c r="E320" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F320" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>LG Washer Main Control Board - EBR42923402</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>newegg.com, lgparts.com washer-parts</t>
         </is>
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="4" t="inlineStr">
+      <c r="A321" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/383eer4001a</t>
         </is>
       </c>
-      <c r="B321" s="4" t="inlineStr">
+      <c r="B321" s="3" t="inlineStr">
         <is>
           <t>383eer4001a</t>
         </is>
       </c>
-      <c r="C321" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D321" s="4" t="inlineStr"/>
-      <c r="E321" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F321" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C321" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D321" s="3" t="inlineStr">
+        <is>
+          <t>LG Washer Service Tool - 383EER4001A</t>
+        </is>
+      </c>
+      <c r="E321" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F321" s="3" t="inlineStr">
+        <is>
+          <t>exact number not found; siblings 383EER4003A/383EER4004A are LG washer service tools (ifixit, ebay)</t>
         </is>
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="4" t="inlineStr">
+      <c r="A322" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/agl73712617</t>
         </is>
       </c>
-      <c r="B322" s="4" t="inlineStr">
+      <c r="B322" t="inlineStr">
         <is>
           <t>agl73712617</t>
         </is>
       </c>
-      <c r="C322" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D322" s="4" t="inlineStr"/>
-      <c r="E322" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F322" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>LG Washer Detergent Dispenser Drawer Panel - AGL73712617</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>lgparts.com Panel Assembly Drawer; ebay.de washer dispenser drawer</t>
         </is>
       </c>
     </row>
@@ -10709,30 +10779,34 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="4" t="inlineStr">
+      <c r="A324" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/add73656053</t>
         </is>
       </c>
-      <c r="B324" s="4" t="inlineStr">
+      <c r="B324" t="inlineStr">
         <is>
           <t>add73656053</t>
         </is>
       </c>
-      <c r="C324" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D324" s="4" t="inlineStr"/>
-      <c r="E324" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F324" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Right Door Assembly - ADD73656053</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>lgparts.com Refrigerator Door Assembly, Right</t>
         </is>
       </c>
     </row>
@@ -10801,30 +10875,34 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="4" t="inlineStr">
+      <c r="A327" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/4987jj2002s</t>
         </is>
       </c>
-      <c r="B327" s="4" t="inlineStr">
+      <c r="B327" t="inlineStr">
         <is>
           <t>4987jj2002s</t>
         </is>
       </c>
-      <c r="C327" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D327" s="4" t="inlineStr"/>
-      <c r="E327" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F327" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Door Gasket Assembly - 4987JJ2002S</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>lgparts.com, appliancepartspros.com; right-side french door gasket; discontinued; replaced by 4987JJ2002E/ADX73270402</t>
         </is>
       </c>
     </row>
@@ -10861,30 +10939,34 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="4" t="inlineStr">
+      <c r="A329" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/adq73853824</t>
         </is>
       </c>
-      <c r="B329" s="4" t="inlineStr">
+      <c r="B329" t="inlineStr">
         <is>
           <t>adq73853824</t>
         </is>
       </c>
-      <c r="C329" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D329" s="4" t="inlineStr"/>
-      <c r="E329" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F329" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Air Filter Assembly - ADQ73853824</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>lgparts.com (air-filter / refrigerator collections), ifixit.com</t>
         </is>
       </c>
     </row>
@@ -10921,58 +11003,66 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="4" t="inlineStr">
+      <c r="A331" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/ead62329122</t>
         </is>
       </c>
-      <c r="B331" s="4" t="inlineStr">
+      <c r="B331" t="inlineStr">
         <is>
           <t>ead62329122</t>
         </is>
       </c>
-      <c r="C331" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D331" s="4" t="inlineStr"/>
-      <c r="E331" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F331" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Power Cord Assembly - EAD62329122</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>lgparts.com, ifixit.com</t>
         </is>
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="4" t="inlineStr">
+      <c r="A332" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/5988ja1001h</t>
         </is>
       </c>
-      <c r="B332" s="4" t="inlineStr">
+      <c r="B332" t="inlineStr">
         <is>
           <t>5988ja1001h</t>
         </is>
       </c>
-      <c r="C332" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D332" s="4" t="inlineStr"/>
-      <c r="E332" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F332" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Ice Maker Control Unit - 5988JA1001H</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>lgparts.com (ice maker control module), ifixit.com, vxb.com (ice maker assembly)</t>
         </is>
       </c>
     </row>
@@ -11009,30 +11099,34 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="4" t="inlineStr">
+      <c r="A334" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/4510ja3003d</t>
         </is>
       </c>
-      <c r="B334" s="4" t="inlineStr">
+      <c r="B334" s="3" t="inlineStr">
         <is>
           <t>4510ja3003d</t>
         </is>
       </c>
-      <c r="C334" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D334" s="4" t="inlineStr"/>
-      <c r="E334" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F334" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C334" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D334" s="3" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Ice Maker Lever - 4510JA3003D</t>
+        </is>
+      </c>
+      <c r="E334" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F334" s="3" t="inlineStr">
+        <is>
+          <t>exact not found; sibling 4510JA3003C ice maker lever (genuinereplacementparts.com)</t>
         </is>
       </c>
     </row>
@@ -11069,86 +11163,98 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="4" t="inlineStr">
+      <c r="A336" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/ebr36832608</t>
         </is>
       </c>
-      <c r="B336" s="4" t="inlineStr">
+      <c r="B336" t="inlineStr">
         <is>
           <t>ebr36832608</t>
         </is>
       </c>
-      <c r="C336" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D336" s="4" t="inlineStr"/>
-      <c r="E336" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F336" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Main PCB Assembly - EBR36832608</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>lgparts.com refrigerator main PCB; siblings EBR36832607/602 (shopjimmy.com)</t>
         </is>
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="4" t="inlineStr">
+      <c r="A337" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/5210ja3005w</t>
         </is>
       </c>
-      <c r="B337" s="4" t="inlineStr">
+      <c r="B337" s="3" t="inlineStr">
         <is>
           <t>5210ja3005w</t>
         </is>
       </c>
-      <c r="C337" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D337" s="4" t="inlineStr"/>
-      <c r="E337" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F337" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C337" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D337" s="3" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Water Tube Assembly - 5210JA3005W</t>
+        </is>
+      </c>
+      <c r="E337" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F337" s="3" t="inlineStr">
+        <is>
+          <t>search failed (rate limit, not retried); 5210JA prefix is LG refrigerator water tubing, unverified</t>
         </is>
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="4" t="inlineStr">
+      <c r="A338" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/aan75368616</t>
         </is>
       </c>
-      <c r="B338" s="4" t="inlineStr">
+      <c r="B338" s="3" t="inlineStr">
         <is>
           <t>aan75368616</t>
         </is>
       </c>
-      <c r="C338" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D338" s="4" t="inlineStr"/>
-      <c r="E338" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F338" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C338" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D338" s="3" t="inlineStr">
+        <is>
+          <t>LG Television Stand Base Assembly - AAN75368616</t>
+        </is>
+      </c>
+      <c r="E338" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F338" s="3" t="inlineStr">
+        <is>
+          <t>exact not found; siblings AAN75368615 TV stand, AAN75368716 base assembly (lgparts)</t>
         </is>
       </c>
     </row>
@@ -11185,30 +11291,34 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="4" t="inlineStr">
+      <c r="A340" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/aba74248404</t>
         </is>
       </c>
-      <c r="B340" s="4" t="inlineStr">
+      <c r="B340" t="inlineStr">
         <is>
           <t>aba74248404</t>
         </is>
       </c>
-      <c r="C340" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D340" s="4" t="inlineStr"/>
-      <c r="E340" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F340" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Evaporator Fan Motor Bracket - ABA74248404</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>lgparts.com Motor Bracket; genuinereplacementparts.com evaporator fan motor bracket assembly</t>
         </is>
       </c>
     </row>
@@ -11245,86 +11355,98 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="4" t="inlineStr">
+      <c r="A342" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/akb73756542</t>
         </is>
       </c>
-      <c r="B342" s="4" t="inlineStr">
+      <c r="B342" t="inlineStr">
         <is>
           <t>akb73756542</t>
         </is>
       </c>
-      <c r="C342" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D342" s="4" t="inlineStr"/>
-      <c r="E342" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F342" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>LG Television Remote Control - AKB73756542</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>lgparts.com, ebay (fits 32LN5700/39LN5700/60PN5700)</t>
         </is>
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="4" t="inlineStr">
+      <c r="A343" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/mcx61961513</t>
         </is>
       </c>
-      <c r="B343" s="4" t="inlineStr">
+      <c r="B343" s="3" t="inlineStr">
         <is>
           <t>mcx61961513</t>
         </is>
       </c>
-      <c r="C343" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D343" s="4" t="inlineStr"/>
-      <c r="E343" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F343" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C343" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D343" s="3" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Drawer - MCX61961513</t>
+        </is>
+      </c>
+      <c r="E343" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F343" s="3" t="inlineStr">
+        <is>
+          <t>exact not found; siblings MCX61961514/15 drawer (lgparts); appliance guessed</t>
         </is>
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="4" t="inlineStr">
+      <c r="A344" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/ebr80321803</t>
         </is>
       </c>
-      <c r="B344" s="4" t="inlineStr">
+      <c r="B344" t="inlineStr">
         <is>
           <t>ebr80321803</t>
         </is>
       </c>
-      <c r="C344" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D344" s="4" t="inlineStr"/>
-      <c r="E344" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F344" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>LG Washer Main PCB Assembly - EBR80321803</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>lgparts.com (fr) washer main circuit board</t>
         </is>
       </c>
     </row>
@@ -11361,58 +11483,66 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="4" t="inlineStr">
+      <c r="A346" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/5989ja1002d</t>
         </is>
       </c>
-      <c r="B346" s="4" t="inlineStr">
+      <c r="B346" t="inlineStr">
         <is>
           <t>5989ja1002d</t>
         </is>
       </c>
-      <c r="C346" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D346" s="4" t="inlineStr"/>
-      <c r="E346" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F346" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Ice Maker Assembly - 5989JA1002D</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>own search rate-limited (not retried); exact number seen in another search as filtersfast.com "LG 5989JA1002D Refrigerator Ice Maker Assembly"</t>
         </is>
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="4" t="inlineStr">
+      <c r="A347" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/may65797102</t>
         </is>
       </c>
-      <c r="B347" s="4" t="inlineStr">
+      <c r="B347" s="3" t="inlineStr">
         <is>
           <t>may65797102</t>
         </is>
       </c>
-      <c r="C347" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D347" s="4" t="inlineStr"/>
-      <c r="E347" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F347" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C347" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D347" s="3" t="inlineStr">
+        <is>
+          <t>LG Washer Detergent Dispenser Box - MAY65797102</t>
+        </is>
+      </c>
+      <c r="E347" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F347" s="3" t="inlineStr">
+        <is>
+          <t>exact not found; sibling MAY65797202 detergent box in lgparts washer-parts</t>
         </is>
       </c>
     </row>
@@ -11481,30 +11611,34 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="4" t="inlineStr">
+      <c r="A350" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/aez74533349</t>
         </is>
       </c>
-      <c r="B350" s="4" t="inlineStr">
+      <c r="B350" s="3" t="inlineStr">
         <is>
           <t>aez74533349</t>
         </is>
       </c>
-      <c r="C350" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D350" s="4" t="inlineStr"/>
-      <c r="E350" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F350" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C350" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D350" s="3" t="inlineStr">
+        <is>
+          <t>LG Range Knob Assembly - AEZ74533349</t>
+        </is>
+      </c>
+      <c r="E350" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F350" s="3" t="inlineStr">
+        <is>
+          <t>exact number not found; siblings AEZ74533347/AEZ74533350 are knob assemblies (lgparts.com, partswarehouse.com); appliance guessed</t>
         </is>
       </c>
     </row>
@@ -11573,30 +11707,34 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="4" t="inlineStr">
+      <c r="A353" s="2" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/ebr34134910</t>
         </is>
       </c>
-      <c r="B353" s="4" t="inlineStr">
+      <c r="B353" s="2" t="inlineStr">
         <is>
           <t>ebr34134910</t>
         </is>
       </c>
-      <c r="C353" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D353" s="4" t="inlineStr"/>
-      <c r="E353" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F353" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C353" s="2" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D353" s="2" t="inlineStr">
+        <is>
+          <t>LG Washer Main Control Board - EBR34134910</t>
+        </is>
+      </c>
+      <c r="E353" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F353" s="2" t="inlineStr">
+        <is>
+          <t>exact number not found; siblings EBR34134902/04/12/23 are washer main PCBs (lgparts.com, shopjimmy.com)</t>
         </is>
       </c>
     </row>
@@ -11697,30 +11835,34 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="4" t="inlineStr">
+      <c r="A357" s="2" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/agl76194023</t>
         </is>
       </c>
-      <c r="B357" s="4" t="inlineStr">
+      <c r="B357" s="2" t="inlineStr">
         <is>
           <t>agl76194023</t>
         </is>
       </c>
-      <c r="C357" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D357" s="4" t="inlineStr"/>
-      <c r="E357" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F357" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C357" s="2" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D357" s="2" t="inlineStr">
+        <is>
+          <t>LG Washer Front Panel Assembly - AGL76194023</t>
+        </is>
+      </c>
+      <c r="E357" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F357" s="2" t="inlineStr">
+        <is>
+          <t>lgparts.com Panel Assembly Front; washer inferred from sibling AGL76194026 washer front panel (ebay.de)</t>
         </is>
       </c>
     </row>
@@ -11789,30 +11931,34 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="4" t="inlineStr">
+      <c r="A360" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/ebr74796477</t>
         </is>
       </c>
-      <c r="B360" s="4" t="inlineStr">
+      <c r="B360" t="inlineStr">
         <is>
           <t>ebr74796477</t>
         </is>
       </c>
-      <c r="C360" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D360" s="4" t="inlineStr"/>
-      <c r="E360" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F360" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Main Control Board - EBR74796477</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>lgparts.com refrigerator electronic control board</t>
         </is>
       </c>
     </row>
@@ -11849,30 +11995,34 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="4" t="inlineStr">
+      <c r="A362" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/afg73249701</t>
         </is>
       </c>
-      <c r="B362" s="4" t="inlineStr">
+      <c r="B362" s="3" t="inlineStr">
         <is>
           <t>afg73249701</t>
         </is>
       </c>
-      <c r="C362" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D362" s="4" t="inlineStr"/>
-      <c r="E362" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F362" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C362" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D362" s="3" t="inlineStr">
+        <is>
+          <t>LG Washer Lid Assembly - AFG73249701</t>
+        </is>
+      </c>
+      <c r="E362" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F362" s="3" t="inlineStr">
+        <is>
+          <t>exact number not found; near numbers AFG73449701 (washer lid, lgparts.com) and AFG73349704 (lid assembly)</t>
         </is>
       </c>
     </row>
@@ -11909,58 +12059,66 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="4" t="inlineStr">
+      <c r="A364" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/aap74271302</t>
         </is>
       </c>
-      <c r="B364" s="4" t="inlineStr">
+      <c r="B364" t="inlineStr">
         <is>
           <t>aap74271302</t>
         </is>
       </c>
-      <c r="C364" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D364" s="4" t="inlineStr"/>
-      <c r="E364" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F364" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Door Basket - AAP74271302</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>lgparts.com refrigerator door basket</t>
         </is>
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="4" t="inlineStr">
+      <c r="A365" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/ebr60388513</t>
         </is>
       </c>
-      <c r="B365" s="4" t="inlineStr">
+      <c r="B365" s="3" t="inlineStr">
         <is>
           <t>ebr60388513</t>
         </is>
       </c>
-      <c r="C365" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D365" s="4" t="inlineStr"/>
-      <c r="E365" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F365" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C365" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D365" s="3" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Main PCB Assembly - EBR60388513</t>
+        </is>
+      </c>
+      <c r="E365" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F365" s="3" t="inlineStr">
+        <is>
+          <t>exact number not found; sibling EBR60388521 is refrigerator PCB (lgparts.com)</t>
         </is>
       </c>
     </row>
@@ -12093,58 +12251,66 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="4" t="inlineStr">
+      <c r="A370" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/mck67395501</t>
         </is>
       </c>
-      <c r="B370" s="4" t="inlineStr">
+      <c r="B370" t="inlineStr">
         <is>
           <t>mck67395501</t>
         </is>
       </c>
-      <c r="C370" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D370" s="4" t="inlineStr"/>
-      <c r="E370" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F370" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>LG Washer Top Cover - MCK67395501</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>lgparts.com (washer top cover panel)</t>
         </is>
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="4" t="inlineStr">
+      <c r="A371" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/eam60991302</t>
         </is>
       </c>
-      <c r="B371" s="4" t="inlineStr">
+      <c r="B371" t="inlineStr">
         <is>
           <t>eam60991302</t>
         </is>
       </c>
-      <c r="C371" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D371" s="4" t="inlineStr"/>
-      <c r="E371" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F371" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>LG Washer Noise Filter Assembly - EAM60991302</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>lgparts.com Washer Filter Assembly; siblings EAM60991301 washer noise filter</t>
         </is>
       </c>
     </row>
@@ -12181,30 +12347,34 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" s="4" t="inlineStr">
+      <c r="A373" s="2" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/add74236501</t>
         </is>
       </c>
-      <c r="B373" s="4" t="inlineStr">
+      <c r="B373" s="2" t="inlineStr">
         <is>
           <t>add74236501</t>
         </is>
       </c>
-      <c r="C373" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D373" s="4" t="inlineStr"/>
-      <c r="E373" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F373" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C373" s="2" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D373" s="2" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Door Assembly - ADD74236501</t>
+        </is>
+      </c>
+      <c r="E373" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F373" s="2" t="inlineStr">
+        <is>
+          <t>ebay.com refrigerator door assembly with handle, seals and hinge; side not stated</t>
         </is>
       </c>
     </row>
@@ -12273,142 +12443,162 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="4" t="inlineStr">
+      <c r="A376" s="2" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/mhl64471705</t>
         </is>
       </c>
-      <c r="B376" s="4" t="inlineStr">
+      <c r="B376" s="2" t="inlineStr">
         <is>
           <t>mhl64471705</t>
         </is>
       </c>
-      <c r="C376" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D376" s="4" t="inlineStr"/>
-      <c r="E376" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F376" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C376" s="2" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D376" s="2" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Glass Shelf - MHL64471705</t>
+        </is>
+      </c>
+      <c r="E376" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F376" s="2" t="inlineStr">
+        <is>
+          <t>spareka.fr (refrigerator glass shelf); siblings MHL64471760/57 glass shelves on lgparts.com</t>
         </is>
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="4" t="inlineStr">
+      <c r="A377" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/ead64545802</t>
         </is>
       </c>
-      <c r="B377" s="4" t="inlineStr">
+      <c r="B377" s="3" t="inlineStr">
         <is>
           <t>ead64545802</t>
         </is>
       </c>
-      <c r="C377" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D377" s="4" t="inlineStr"/>
-      <c r="E377" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F377" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C377" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D377" s="3" t="inlineStr">
+        <is>
+          <t>LG Wire Harness Assembly - EAD64545802</t>
+        </is>
+      </c>
+      <c r="E377" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F377" s="3" t="inlineStr">
+        <is>
+          <t>Appliance not identified. exact not found; EAD series siblings are harness assemblies (lgparts)</t>
         </is>
       </c>
     </row>
     <row r="378">
-      <c r="A378" s="4" t="inlineStr">
+      <c r="A378" s="2" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/aez75994615</t>
         </is>
       </c>
-      <c r="B378" s="4" t="inlineStr">
+      <c r="B378" s="2" t="inlineStr">
         <is>
           <t>aez75994615</t>
         </is>
       </c>
-      <c r="C378" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D378" s="4" t="inlineStr"/>
-      <c r="E378" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F378" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C378" s="2" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D378" s="2" t="inlineStr">
+        <is>
+          <t>LG Range Knob Assembly - AEZ75994615</t>
+        </is>
+      </c>
+      <c r="E378" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F378" s="2" t="inlineStr">
+        <is>
+          <t>lgparts.com knob assembly; appliance not stated (kitchen or laundry), range guessed</t>
         </is>
       </c>
     </row>
     <row r="379">
-      <c r="A379" s="4" t="inlineStr">
+      <c r="A379" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/add73936020</t>
         </is>
       </c>
-      <c r="B379" s="4" t="inlineStr">
+      <c r="B379" s="3" t="inlineStr">
         <is>
           <t>add73936020</t>
         </is>
       </c>
-      <c r="C379" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D379" s="4" t="inlineStr"/>
-      <c r="E379" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F379" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C379" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D379" s="3" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Door Foam Assembly - ADD73936020</t>
+        </is>
+      </c>
+      <c r="E379" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F379" s="3" t="inlineStr">
+        <is>
+          <t>exact number not found; siblings ADD73936027 (door foam assembly) and ADD73936016 (door panel) on genuinereplacementparts.com</t>
         </is>
       </c>
     </row>
     <row r="380">
-      <c r="A380" s="4" t="inlineStr">
+      <c r="A380" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/aht73493943</t>
         </is>
       </c>
-      <c r="B380" s="4" t="inlineStr">
+      <c r="B380" s="3" t="inlineStr">
         <is>
           <t>aht73493943</t>
         </is>
       </c>
-      <c r="C380" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D380" s="4" t="inlineStr"/>
-      <c r="E380" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F380" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C380" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D380" s="3" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Freezer Shelf Assembly - AHT73493943</t>
+        </is>
+      </c>
+      <c r="E380" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F380" s="3" t="inlineStr">
+        <is>
+          <t>exact not found; siblings AHT73493936/37/38/41 freezer shelf (lgparts, shopjimmy, filtersfast)</t>
         </is>
       </c>
     </row>
@@ -12477,86 +12667,98 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" s="4" t="inlineStr">
+      <c r="A383" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/agm73551661</t>
         </is>
       </c>
-      <c r="B383" s="4" t="inlineStr">
+      <c r="B383" s="3" t="inlineStr">
         <is>
           <t>agm73551661</t>
         </is>
       </c>
-      <c r="C383" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D383" s="4" t="inlineStr"/>
-      <c r="E383" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F383" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C383" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D383" s="3" t="inlineStr">
+        <is>
+          <t>LG Range Control Panel Assembly - AGM73551661</t>
+        </is>
+      </c>
+      <c r="E383" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F383" s="3" t="inlineStr">
+        <is>
+          <t>exact number not found; siblings AGM73551660/619 are range control panels (lgparts.com)</t>
         </is>
       </c>
     </row>
     <row r="384">
-      <c r="A384" s="4" t="inlineStr">
+      <c r="A384" s="2" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/aaa76555332</t>
         </is>
       </c>
-      <c r="B384" s="4" t="inlineStr">
+      <c r="B384" s="2" t="inlineStr">
         <is>
           <t>aaa76555332</t>
         </is>
       </c>
-      <c r="C384" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D384" s="4" t="inlineStr"/>
-      <c r="E384" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F384" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C384" s="2" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D384" s="2" t="inlineStr">
+        <is>
+          <t>LG Washer Drain Connector Kit - AAA76555332</t>
+        </is>
+      </c>
+      <c r="E384" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F384" s="2" t="inlineStr">
+        <is>
+          <t>lgparts.com (drain connector kit, in washer-dryer combo parts collection); sibling AAA76555302 washer accessory kit</t>
         </is>
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="4" t="inlineStr">
+      <c r="A385" s="2" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/ead65212502</t>
         </is>
       </c>
-      <c r="B385" s="4" t="inlineStr">
+      <c r="B385" s="2" t="inlineStr">
         <is>
           <t>ead65212502</t>
         </is>
       </c>
-      <c r="C385" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D385" s="4" t="inlineStr"/>
-      <c r="E385" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F385" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C385" s="2" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D385" s="2" t="inlineStr">
+        <is>
+          <t>LG Washer Power Cord - EAD65212502</t>
+        </is>
+      </c>
+      <c r="E385" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F385" s="2" t="inlineStr">
+        <is>
+          <t>only a third-party mirror listing names it LG Washing Machine Power Cord; no LG source</t>
         </is>
       </c>
     </row>
@@ -12625,58 +12827,66 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" s="4" t="inlineStr">
+      <c r="A388" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/ebr30368910</t>
         </is>
       </c>
-      <c r="B388" s="4" t="inlineStr">
+      <c r="B388" s="3" t="inlineStr">
         <is>
           <t>ebr30368910</t>
         </is>
       </c>
-      <c r="C388" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D388" s="4" t="inlineStr"/>
-      <c r="E388" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F388" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C388" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D388" s="3" t="inlineStr">
+        <is>
+          <t>LG Washer Display PCB Assembly - EBR30368910</t>
+        </is>
+      </c>
+      <c r="E388" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F388" s="3" t="inlineStr">
+        <is>
+          <t>exact number not found; siblings EBR30368927 (washer display PCB, shopjimmy.com) and EBR30368902 (display PCB, lgparts.com)</t>
         </is>
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="4" t="inlineStr">
+      <c r="A389" s="2" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/afg73629723</t>
         </is>
       </c>
-      <c r="B389" s="4" t="inlineStr">
+      <c r="B389" s="2" t="inlineStr">
         <is>
           <t>afg73629723</t>
         </is>
       </c>
-      <c r="C389" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D389" s="4" t="inlineStr"/>
-      <c r="E389" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F389" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C389" s="2" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D389" s="2" t="inlineStr">
+        <is>
+          <t>LG Washer Glass Lid Assembly - AFG73629723</t>
+        </is>
+      </c>
+      <c r="E389" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F389" s="2" t="inlineStr">
+        <is>
+          <t>lgparts.com (lid assembly); siblings AFG73629722/AFG73629701 washer glass lids (ebay, good-appliance.com)</t>
         </is>
       </c>
     </row>
@@ -12713,30 +12923,34 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" s="4" t="inlineStr">
+      <c r="A391" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/aan75869332</t>
         </is>
       </c>
-      <c r="B391" s="4" t="inlineStr">
+      <c r="B391" s="3" t="inlineStr">
         <is>
           <t>aan75869332</t>
         </is>
       </c>
-      <c r="C391" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D391" s="4" t="inlineStr"/>
-      <c r="E391" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F391" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C391" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D391" s="3" t="inlineStr">
+        <is>
+          <t>LG Television Stand Base - AAN75869332</t>
+        </is>
+      </c>
+      <c r="E391" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F391" s="3" t="inlineStr">
+        <is>
+          <t>exact not found; siblings AAN75869331/33 base (lgparts); TV inferred</t>
         </is>
       </c>
     </row>
@@ -12773,86 +12987,98 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" s="4" t="inlineStr">
+      <c r="A393" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/adc73685905</t>
         </is>
       </c>
-      <c r="B393" s="4" t="inlineStr">
+      <c r="B393" t="inlineStr">
         <is>
           <t>adc73685905</t>
         </is>
       </c>
-      <c r="C393" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D393" s="4" t="inlineStr"/>
-      <c r="E393" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F393" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>LG Washer Door Assembly - ADC73685905</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>lgparts.com washer door assembly</t>
         </is>
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="4" t="inlineStr">
+      <c r="A394" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/ebr86093701</t>
         </is>
       </c>
-      <c r="B394" s="4" t="inlineStr">
+      <c r="B394" t="inlineStr">
         <is>
           <t>ebr86093701</t>
         </is>
       </c>
-      <c r="C394" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D394" s="4" t="inlineStr"/>
-      <c r="E394" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F394" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Electronic Control Board - EBR86093701</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>lgparts.com, newegg.com (fits LFXS28596)</t>
         </is>
       </c>
     </row>
     <row r="395">
-      <c r="A395" s="4" t="inlineStr">
+      <c r="A395" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/agu30012402</t>
         </is>
       </c>
-      <c r="B395" s="4" t="inlineStr">
+      <c r="B395" t="inlineStr">
         <is>
           <t>agu30012402</t>
         </is>
       </c>
-      <c r="C395" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D395" s="4" t="inlineStr"/>
-      <c r="E395" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F395" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>LG Range Main Top Plate Assembly - AGU30012402</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>lgparts.com Range Main Top / Range Plate Assembly</t>
         </is>
       </c>
     </row>
@@ -12921,142 +13147,162 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" s="4" t="inlineStr">
+      <c r="A398" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/eau65058305</t>
         </is>
       </c>
-      <c r="B398" s="4" t="inlineStr">
+      <c r="B398" t="inlineStr">
         <is>
           <t>eau65058305</t>
         </is>
       </c>
-      <c r="C398" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D398" s="4" t="inlineStr"/>
-      <c r="E398" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F398" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>LG Refrigerator DC Fan Motor - EAU65058305</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>lgparts.com refrigerator DC motor; superseded by EAU65058511 per partswarehouse.com</t>
         </is>
       </c>
     </row>
     <row r="399">
-      <c r="A399" s="4" t="inlineStr">
+      <c r="A399" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/agr75445324</t>
         </is>
       </c>
-      <c r="B399" s="4" t="inlineStr">
+      <c r="B399" s="3" t="inlineStr">
         <is>
           <t>agr75445324</t>
         </is>
       </c>
-      <c r="C399" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D399" s="4" t="inlineStr"/>
-      <c r="E399" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F399" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C399" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D399" s="3" t="inlineStr">
+        <is>
+          <t>LG Vacuum Telescopic Pipe Assembly - AGR75445324</t>
+        </is>
+      </c>
+      <c r="E399" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F399" s="3" t="inlineStr">
+        <is>
+          <t>exact number not found; sibling AGR75445325 telescopic pipe assembly on lgparts.com (stick vacuum wand, inferred)</t>
         </is>
       </c>
     </row>
     <row r="400">
-      <c r="A400" s="4" t="inlineStr">
+      <c r="A400" s="2" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/ebr31002605</t>
         </is>
       </c>
-      <c r="B400" s="4" t="inlineStr">
+      <c r="B400" s="2" t="inlineStr">
         <is>
           <t>ebr31002605</t>
         </is>
       </c>
-      <c r="C400" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D400" s="4" t="inlineStr"/>
-      <c r="E400" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F400" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C400" s="2" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D400" s="2" t="inlineStr">
+        <is>
+          <t>LG Washer Main Control Board - EBR31002605</t>
+        </is>
+      </c>
+      <c r="E400" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F400" s="2" t="inlineStr">
+        <is>
+          <t>lgparts.com washer collection + ebay.de washer; genuinereplacementparts.com says dryer main PCB (conflict)</t>
         </is>
       </c>
     </row>
     <row r="401">
-      <c r="A401" s="4" t="inlineStr">
+      <c r="A401" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/5901a20050a</t>
         </is>
       </c>
-      <c r="B401" s="4" t="inlineStr">
+      <c r="B401" t="inlineStr">
         <is>
           <t>5901a20050a</t>
         </is>
       </c>
-      <c r="C401" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D401" s="4" t="inlineStr"/>
-      <c r="E401" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F401" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>LG Air Conditioner Cross Flow Fan Assembly - 5901A20050A</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>supplyhouse.com, hnkparts.com, lgparts.com (evaporator fan blade); fits LP093HD3A, LP150CED</t>
         </is>
       </c>
     </row>
     <row r="402">
-      <c r="A402" s="4" t="inlineStr">
+      <c r="A402" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/3551dd2001e</t>
         </is>
       </c>
-      <c r="B402" s="4" t="inlineStr">
+      <c r="B402" t="inlineStr">
         <is>
           <t>3551dd2001e</t>
         </is>
       </c>
-      <c r="C402" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D402" s="4" t="inlineStr"/>
-      <c r="E402" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F402" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>LG Dishwasher Lower Cover - 3551DD2001E</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>lgparts.com (dishwasher lower cover)</t>
         </is>
       </c>
     </row>
@@ -13125,86 +13371,98 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405" s="4" t="inlineStr">
+      <c r="A405" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/eac63382205</t>
         </is>
       </c>
-      <c r="B405" s="4" t="inlineStr">
+      <c r="B405" t="inlineStr">
         <is>
           <t>eac63382205</t>
         </is>
       </c>
-      <c r="C405" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D405" s="4" t="inlineStr"/>
-      <c r="E405" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F405" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>LG Vacuum Battery - EAC63382205</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>lgparts.com vacuum cleaner battery</t>
         </is>
       </c>
     </row>
     <row r="406">
-      <c r="A406" s="4" t="inlineStr">
+      <c r="A406" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/meb62494914</t>
         </is>
       </c>
-      <c r="B406" s="4" t="inlineStr">
+      <c r="B406" t="inlineStr">
         <is>
           <t>meb62494914</t>
         </is>
       </c>
-      <c r="C406" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D406" s="4" t="inlineStr"/>
-      <c r="E406" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F406" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>LG Range Door Handle - MEB62494914</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>lgparts.com (fr) range collection door handle</t>
         </is>
       </c>
     </row>
     <row r="407">
-      <c r="A407" s="4" t="inlineStr">
+      <c r="A407" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/adp36665705</t>
         </is>
       </c>
-      <c r="B407" s="4" t="inlineStr">
+      <c r="B407" t="inlineStr">
         <is>
           <t>adp36665705</t>
         </is>
       </c>
-      <c r="C407" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D407" s="4" t="inlineStr"/>
-      <c r="E407" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F407" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Condenser Fan Blade - ADP36665705</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>lgparts.com</t>
         </is>
       </c>
     </row>
@@ -13273,58 +13531,66 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410" s="4" t="inlineStr">
+      <c r="A410" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/3391ja1082f</t>
         </is>
       </c>
-      <c r="B410" s="4" t="inlineStr">
+      <c r="B410" t="inlineStr">
         <is>
           <t>3391ja1082f</t>
         </is>
       </c>
-      <c r="C410" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D410" s="4" t="inlineStr"/>
-      <c r="E410" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F410" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Crisper Drawer - 3391JA1082F</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>lgparts.com crisper drawer / vegetable tray</t>
         </is>
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="4" t="inlineStr">
+      <c r="A411" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/eav64012007</t>
         </is>
       </c>
-      <c r="B411" s="4" t="inlineStr">
+      <c r="B411" t="inlineStr">
         <is>
           <t>eav64012007</t>
         </is>
       </c>
-      <c r="C411" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D411" s="4" t="inlineStr"/>
-      <c r="E411" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F411" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>LG Range Display Board - EAV64012007</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>lgparts.com, third-party listing LG Range Display Board</t>
         </is>
       </c>
     </row>
@@ -13361,30 +13627,34 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" s="4" t="inlineStr">
+      <c r="A413" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/mck70055606</t>
         </is>
       </c>
-      <c r="B413" s="4" t="inlineStr">
+      <c r="B413" s="3" t="inlineStr">
         <is>
           <t>mck70055606</t>
         </is>
       </c>
-      <c r="C413" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D413" s="4" t="inlineStr"/>
-      <c r="E413" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F413" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C413" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D413" s="3" t="inlineStr">
+        <is>
+          <t>LG Washer Top Cover - MCK70055606</t>
+        </is>
+      </c>
+      <c r="E413" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F413" s="3" t="inlineStr">
+        <is>
+          <t>exact number not found; sibling MCK70055604 washer top cover on lgparts.com</t>
         </is>
       </c>
     </row>
@@ -13485,30 +13755,34 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" s="4" t="inlineStr">
+      <c r="A417" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/add73697421</t>
         </is>
       </c>
-      <c r="B417" s="4" t="inlineStr">
+      <c r="B417" s="3" t="inlineStr">
         <is>
           <t>add73697421</t>
         </is>
       </c>
-      <c r="C417" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D417" s="4" t="inlineStr"/>
-      <c r="E417" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F417" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C417" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D417" s="3" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Door Foam Assembly - ADD73697421</t>
+        </is>
+      </c>
+      <c r="E417" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F417" s="3" t="inlineStr">
+        <is>
+          <t>exact not found; ADD7429xx siblings are refrigerator door foam assemblies; guess</t>
         </is>
       </c>
     </row>
@@ -13545,30 +13819,34 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" s="4" t="inlineStr">
+      <c r="A419" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/eay65689411</t>
         </is>
       </c>
-      <c r="B419" s="4" t="inlineStr">
+      <c r="B419" t="inlineStr">
         <is>
           <t>eay65689411</t>
         </is>
       </c>
-      <c r="C419" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D419" s="4" t="inlineStr"/>
-      <c r="E419" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F419" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>LG Television Power Supply Assembly - EAY65689411</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>lgparts.com television collection; ebay.de lists OLED65B1/OLED65C1/OLED65CX9</t>
         </is>
       </c>
     </row>
@@ -13637,142 +13915,162 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422" s="4" t="inlineStr">
+      <c r="A422" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/5859ea1004e</t>
         </is>
       </c>
-      <c r="B422" s="4" t="inlineStr">
+      <c r="B422" t="inlineStr">
         <is>
           <t>5859ea1004e</t>
         </is>
       </c>
-      <c r="C422" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D422" s="4" t="inlineStr"/>
-      <c r="E422" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F422" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>LG Washer Drain Pump Assembly - 5859EA1004E</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>lgparts.com, newegg.com; interchangeable with 5859EA1004G/F/Q/P, AHA74333302</t>
         </is>
       </c>
     </row>
     <row r="423">
-      <c r="A423" s="4" t="inlineStr">
+      <c r="A423" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/aju73432806</t>
         </is>
       </c>
-      <c r="B423" s="4" t="inlineStr">
+      <c r="B423" t="inlineStr">
         <is>
           <t>aju73432806</t>
         </is>
       </c>
-      <c r="C423" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D423" s="4" t="inlineStr"/>
-      <c r="E423" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F423" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Water Inlet Valve Assembly - AJU73432806</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>lgparts.com refrigerator-parts, ifixit.com</t>
         </is>
       </c>
     </row>
     <row r="424">
-      <c r="A424" s="4" t="inlineStr">
+      <c r="A424" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/ebr86283105</t>
         </is>
       </c>
-      <c r="B424" s="4" t="inlineStr">
+      <c r="B424" t="inlineStr">
         <is>
           <t>ebr86283105</t>
         </is>
       </c>
-      <c r="C424" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D424" s="4" t="inlineStr"/>
-      <c r="E424" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F424" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>LG Washer Main Control Board - EBR86283105</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>newegg.com washer control board assembly (with EBR86692720); siblings EBR86283106/107 washer boards (shopjimmy.com, lgparts.com)</t>
         </is>
       </c>
     </row>
     <row r="425">
-      <c r="A425" s="4" t="inlineStr">
+      <c r="A425" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/mjs62595101</t>
         </is>
       </c>
-      <c r="B425" s="4" t="inlineStr">
+      <c r="B425" s="3" t="inlineStr">
         <is>
           <t>mjs62595101</t>
         </is>
       </c>
-      <c r="C425" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D425" s="4" t="inlineStr"/>
-      <c r="E425" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F425" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C425" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D425" s="3" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Defrost Drain Pan - MJS62595101</t>
+        </is>
+      </c>
+      <c r="E425" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F425" s="3" t="inlineStr">
+        <is>
+          <t>exact number not found; siblings MJS62595201 (drain pan, lgparts.com) and MJS62591901 (defrost drain pan)</t>
         </is>
       </c>
     </row>
     <row r="426">
-      <c r="A426" s="4" t="inlineStr">
+      <c r="A426" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/5209el1001d</t>
         </is>
       </c>
-      <c r="B426" s="4" t="inlineStr">
+      <c r="B426" t="inlineStr">
         <is>
           <t>5209el1001d</t>
         </is>
       </c>
-      <c r="C426" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D426" s="4" t="inlineStr"/>
-      <c r="E426" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F426" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>LG Dryer Duct Assembly - 5209EL1001D</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>lgparts.com dryer duct; searspartsdirect says replaced by 5209EL1001E</t>
         </is>
       </c>
     </row>
@@ -13841,58 +14139,66 @@
       </c>
     </row>
     <row r="429">
-      <c r="A429" s="4" t="inlineStr">
+      <c r="A429" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/abq76121034</t>
         </is>
       </c>
-      <c r="B429" s="4" t="inlineStr">
+      <c r="B429" t="inlineStr">
         <is>
           <t>abq76121034</t>
         </is>
       </c>
-      <c r="C429" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D429" s="4" t="inlineStr"/>
-      <c r="E429" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F429" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>LG Refrigerator PCB Case Assembly - ABQ76121034</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>lgparts.com Refrigerator Case Assembly, Pcb</t>
         </is>
       </c>
     </row>
     <row r="430">
-      <c r="A430" s="4" t="inlineStr">
+      <c r="A430" s="2" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/5006el3001d</t>
         </is>
       </c>
-      <c r="B430" s="4" t="inlineStr">
+      <c r="B430" s="2" t="inlineStr">
         <is>
           <t>5006el3001d</t>
         </is>
       </c>
-      <c r="C430" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D430" s="4" t="inlineStr"/>
-      <c r="E430" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F430" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C430" s="2" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D430" s="2" t="inlineStr">
+        <is>
+          <t>LG Dryer Vent Hole Cap - 5006EL3001D</t>
+        </is>
+      </c>
+      <c r="E430" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F430" s="2" t="inlineStr">
+        <is>
+          <t>exact number not found; siblings 5006EL3001S/5006EL3001H dryer caps (lgparts.com, ebay)</t>
         </is>
       </c>
     </row>
@@ -13961,30 +14267,34 @@
       </c>
     </row>
     <row r="433">
-      <c r="A433" s="4" t="inlineStr">
+      <c r="A433" s="2" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/aez75853710</t>
         </is>
       </c>
-      <c r="B433" s="4" t="inlineStr">
+      <c r="B433" s="2" t="inlineStr">
         <is>
           <t>aez75853710</t>
         </is>
       </c>
-      <c r="C433" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D433" s="4" t="inlineStr"/>
-      <c r="E433" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F433" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C433" s="2" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D433" s="2" t="inlineStr">
+        <is>
+          <t>LG Range Knob Assembly - AEZ75853710</t>
+        </is>
+      </c>
+      <c r="E433" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F433" s="2" t="inlineStr">
+        <is>
+          <t>only third-party mirror listing (oven range knob); siblings AEZ75853709/11 range knob (lgparts)</t>
         </is>
       </c>
     </row>
@@ -14053,198 +14363,226 @@
       </c>
     </row>
     <row r="436">
-      <c r="A436" s="4" t="inlineStr">
+      <c r="A436" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/mds66290810</t>
         </is>
       </c>
-      <c r="B436" s="4" t="inlineStr">
+      <c r="B436" s="3" t="inlineStr">
         <is>
           <t>mds66290810</t>
         </is>
       </c>
-      <c r="C436" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D436" s="4" t="inlineStr"/>
-      <c r="E436" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F436" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C436" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D436" s="3" t="inlineStr">
+        <is>
+          <t>LG Washer Door Gasket - MDS66290810</t>
+        </is>
+      </c>
+      <c r="E436" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F436" s="3" t="inlineStr">
+        <is>
+          <t>exact number not found; MDS662908xx siblings are washer door gaskets/boots (lgparts.com, ereplacementparts.com)</t>
         </is>
       </c>
     </row>
     <row r="437">
-      <c r="A437" s="4" t="inlineStr">
+      <c r="A437" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/4417ea1002y</t>
         </is>
       </c>
-      <c r="B437" s="4" t="inlineStr">
+      <c r="B437" t="inlineStr">
         <is>
           <t>4417ea1002y</t>
         </is>
       </c>
-      <c r="C437" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D437" s="4" t="inlineStr"/>
-      <c r="E437" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F437" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>LG Washer Motor Stator Assembly - 4417EA1002Y</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>lgparts.com, lgcanadaparts.com, appliancepartspros.com; replaces 4417FA1994F</t>
         </is>
       </c>
     </row>
     <row r="438">
-      <c r="A438" s="4" t="inlineStr">
+      <c r="A438" s="2" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/3391jj2018d</t>
         </is>
       </c>
-      <c r="B438" s="4" t="inlineStr">
+      <c r="B438" s="2" t="inlineStr">
         <is>
           <t>3391jj2018d</t>
         </is>
       </c>
-      <c r="C438" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D438" s="4" t="inlineStr"/>
-      <c r="E438" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F438" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C438" s="2" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D438" s="2" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Deli Drawer - 3391JJ2018D</t>
+        </is>
+      </c>
+      <c r="E438" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F438" s="2" t="inlineStr">
+        <is>
+          <t>filtersfast.com listing names it deli drawer; no LG page found</t>
         </is>
       </c>
     </row>
     <row r="439">
-      <c r="A439" s="4" t="inlineStr">
+      <c r="A439" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/mgc66180306</t>
         </is>
       </c>
-      <c r="B439" s="4" t="inlineStr">
+      <c r="B439" t="inlineStr">
         <is>
           <t>mgc66180306</t>
         </is>
       </c>
-      <c r="C439" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D439" s="4" t="inlineStr"/>
-      <c r="E439" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F439" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>LG Range Drawer Panel - MGC66180306</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>lgparts.com range collection drawer panel</t>
         </is>
       </c>
     </row>
     <row r="440">
-      <c r="A440" s="4" t="inlineStr">
+      <c r="A440" s="2" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/mbe62162902</t>
         </is>
       </c>
-      <c r="B440" s="4" t="inlineStr">
+      <c r="B440" s="2" t="inlineStr">
         <is>
           <t>mbe62162902</t>
         </is>
       </c>
-      <c r="C440" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D440" s="4" t="inlineStr"/>
-      <c r="E440" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F440" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C440" s="2" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D440" s="2" t="inlineStr">
+        <is>
+          <t>LG Range Surface Burner - MBE62162902</t>
+        </is>
+      </c>
+      <c r="E440" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F440" s="2" t="inlineStr">
+        <is>
+          <t>exact number not found; sibling MBE62162901 range burner on lgparts.com</t>
         </is>
       </c>
     </row>
     <row r="441">
-      <c r="A441" s="4" t="inlineStr">
+      <c r="A441" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/meb41909001</t>
         </is>
       </c>
-      <c r="B441" s="4" t="inlineStr">
+      <c r="B441" s="3" t="inlineStr">
         <is>
           <t>meb41909001</t>
         </is>
       </c>
-      <c r="C441" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D441" s="4" t="inlineStr"/>
-      <c r="E441" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F441" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C441" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D441" s="3" t="inlineStr">
+        <is>
+          <t>LG Range Door Handle - MEB41909001</t>
+        </is>
+      </c>
+      <c r="E441" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F441" s="3" t="inlineStr">
+        <is>
+          <t>exact not found; MEB41909002 in lgparts oven collection, MEB41908101 microwave door handle; guess</t>
         </is>
       </c>
     </row>
     <row r="442">
-      <c r="A442" s="4" t="inlineStr">
+      <c r="A442" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/abh74399727</t>
         </is>
       </c>
-      <c r="B442" s="4" t="inlineStr">
+      <c r="B442" t="inlineStr">
         <is>
           <t>abh74399727</t>
         </is>
       </c>
-      <c r="C442" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D442" s="4" t="inlineStr"/>
-      <c r="E442" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F442" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Dispenser Button Assembly - ABH74399727</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>lgparts.com refrigerator button; sibling ABH74399728 button assembly</t>
         </is>
       </c>
     </row>
@@ -14313,114 +14651,130 @@
       </c>
     </row>
     <row r="445">
-      <c r="A445" s="4" t="inlineStr">
+      <c r="A445" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/eau62145211</t>
         </is>
       </c>
-      <c r="B445" s="4" t="inlineStr">
+      <c r="B445" t="inlineStr">
         <is>
           <t>eau62145211</t>
         </is>
       </c>
-      <c r="C445" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D445" s="4" t="inlineStr"/>
-      <c r="E445" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F445" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Fresh Food Fan Motor - EAU62145211</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>lgparts.com</t>
         </is>
       </c>
     </row>
     <row r="446">
-      <c r="A446" s="4" t="inlineStr">
+      <c r="A446" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/adc49436905</t>
         </is>
       </c>
-      <c r="B446" s="4" t="inlineStr">
+      <c r="B446" s="3" t="inlineStr">
         <is>
           <t>adc49436905</t>
         </is>
       </c>
-      <c r="C446" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D446" s="4" t="inlineStr"/>
-      <c r="E446" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F446" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C446" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D446" s="3" t="inlineStr">
+        <is>
+          <t>LG Door Assembly - ADC49436905</t>
+        </is>
+      </c>
+      <c r="E446" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F446" s="3" t="inlineStr">
+        <is>
+          <t>Appliance not identified. exact not found; ADC prefix siblings are door assemblies (lgparts)</t>
         </is>
       </c>
     </row>
     <row r="447">
-      <c r="A447" s="4" t="inlineStr">
+      <c r="A447" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/3751dd1002c</t>
         </is>
       </c>
-      <c r="B447" s="4" t="inlineStr">
+      <c r="B447" t="inlineStr">
         <is>
           <t>3751dd1002c</t>
         </is>
       </c>
-      <c r="C447" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D447" s="4" t="inlineStr"/>
-      <c r="E447" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F447" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>LG Dishwasher Dish Rack - 3751DD1002C</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>lgparts.com LG Dishwasher Rack; upper/lower not stated</t>
         </is>
       </c>
     </row>
     <row r="448">
-      <c r="A448" s="4" t="inlineStr">
+      <c r="A448" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/6877er1016p</t>
         </is>
       </c>
-      <c r="B448" s="4" t="inlineStr">
+      <c r="B448" t="inlineStr">
         <is>
           <t>6877er1016p</t>
         </is>
       </c>
-      <c r="C448" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D448" s="4" t="inlineStr"/>
-      <c r="E448" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F448" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>LG Washer Motor Wire Harness - 6877ER1016P</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>lgparts.com; siblings 6877ER1016F/S/B multi harness (filtersfast.com, ebay)</t>
         </is>
       </c>
     </row>
@@ -14457,86 +14811,98 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450" s="4" t="inlineStr">
+      <c r="A450" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/mkj39170828</t>
         </is>
       </c>
-      <c r="B450" s="4" t="inlineStr">
+      <c r="B450" t="inlineStr">
         <is>
           <t>mkj39170828</t>
         </is>
       </c>
-      <c r="C450" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D450" s="4" t="inlineStr"/>
-      <c r="E450" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F450" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>LG Television Service Remote Control - MKJ39170828</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>ebay.com/ebay.de factory SVC service remote for LG LCD/LED TV</t>
         </is>
       </c>
     </row>
     <row r="451">
-      <c r="A451" s="4" t="inlineStr">
+      <c r="A451" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/afg73249702</t>
         </is>
       </c>
-      <c r="B451" s="4" t="inlineStr">
+      <c r="B451" t="inlineStr">
         <is>
           <t>afg73249702</t>
         </is>
       </c>
-      <c r="C451" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D451" s="4" t="inlineStr"/>
-      <c r="E451" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F451" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>LG Washer Lid Assembly - AFG73249702</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>lgparts.com washer lid covering tub opening</t>
         </is>
       </c>
     </row>
     <row r="452">
-      <c r="A452" s="4" t="inlineStr">
+      <c r="A452" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/adj75472601</t>
         </is>
       </c>
-      <c r="B452" s="4" t="inlineStr">
+      <c r="B452" t="inlineStr">
         <is>
           <t>adj75472601</t>
         </is>
       </c>
-      <c r="C452" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D452" s="4" t="inlineStr"/>
-      <c r="E452" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F452" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Multi Duct Assembly - ADJ75472601</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>lgparts.com, ebay (fits LRMDS3006S); sibling ADJ75472620</t>
         </is>
       </c>
     </row>
@@ -14637,86 +15003,98 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" s="4" t="inlineStr">
+      <c r="A456" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/ajb73816028</t>
         </is>
       </c>
-      <c r="B456" s="4" t="inlineStr">
+      <c r="B456" t="inlineStr">
         <is>
           <t>ajb73816028</t>
         </is>
       </c>
-      <c r="C456" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D456" s="4" t="inlineStr"/>
-      <c r="E456" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F456" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>LG Washer Motor Stator Assembly - AJB73816028</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>shopjimmy.com stator for WM3700HWA etc.; possibly paired with AJB73816029</t>
         </is>
       </c>
     </row>
     <row r="457">
-      <c r="A457" s="4" t="inlineStr">
+      <c r="A457" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/aeb73944701</t>
         </is>
       </c>
-      <c r="B457" s="4" t="inlineStr">
+      <c r="B457" t="inlineStr">
         <is>
           <t>aeb73944701</t>
         </is>
       </c>
-      <c r="C457" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D457" s="4" t="inlineStr"/>
-      <c r="E457" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F457" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Fan Grille Assembly - AEB73944701</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>ifixit.com, partswarehouse.com; replaces ADJ72911301, ADJ72911303, ADJ73832202, AEB36999401, AEB36999402, AEB73944601, MDX42267301</t>
         </is>
       </c>
     </row>
     <row r="458">
-      <c r="A458" s="4" t="inlineStr">
+      <c r="A458" s="2" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/tca36811404</t>
         </is>
       </c>
-      <c r="B458" s="4" t="inlineStr">
+      <c r="B458" s="2" t="inlineStr">
         <is>
           <t>tca36811404</t>
         </is>
       </c>
-      <c r="C458" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D458" s="4" t="inlineStr"/>
-      <c r="E458" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F458" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C458" s="2" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D458" s="2" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Compressor - TCA36811404</t>
+        </is>
+      </c>
+      <c r="E458" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F458" s="2" t="inlineStr">
+        <is>
+          <t>lgparts.com lists exact number in refrigerator collection without name; siblings TCA36811409/32/15 are refrigerator compressors</t>
         </is>
       </c>
     </row>
@@ -14753,30 +15131,34 @@
       </c>
     </row>
     <row r="460">
-      <c r="A460" s="4" t="inlineStr">
+      <c r="A460" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/ajp76401602</t>
         </is>
       </c>
-      <c r="B460" s="4" t="inlineStr">
+      <c r="B460" s="3" t="inlineStr">
         <is>
           <t>ajp76401602</t>
         </is>
       </c>
-      <c r="C460" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D460" s="4" t="inlineStr"/>
-      <c r="E460" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F460" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C460" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D460" s="3" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Drawer Tray Assembly - AJP76401602</t>
+        </is>
+      </c>
+      <c r="E460" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F460" s="3" t="inlineStr">
+        <is>
+          <t>exact not found; siblings AJP76401604/06 refrigerator drawer tray (lgparts)</t>
         </is>
       </c>
     </row>
@@ -14813,30 +15195,34 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462" s="4" t="inlineStr">
+      <c r="A462" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/eau63503703</t>
         </is>
       </c>
-      <c r="B462" s="4" t="inlineStr">
+      <c r="B462" s="3" t="inlineStr">
         <is>
           <t>eau63503703</t>
         </is>
       </c>
-      <c r="C462" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D462" s="4" t="inlineStr"/>
-      <c r="E462" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F462" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C462" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D462" s="3" t="inlineStr">
+        <is>
+          <t>LG Refrigerator DC Fan Motor - EAU63503703</t>
+        </is>
+      </c>
+      <c r="E462" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F462" s="3" t="inlineStr">
+        <is>
+          <t>no dedicated listing; siblings EAU63503702/704 are refrigerator DC motors (lgparts.com), EAU63503709 evaporator fan motor</t>
         </is>
       </c>
     </row>
@@ -14905,114 +15291,130 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465" s="4" t="inlineStr">
+      <c r="A465" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/ebr78538807</t>
         </is>
       </c>
-      <c r="B465" s="4" t="inlineStr">
+      <c r="B465" t="inlineStr">
         <is>
           <t>ebr78538807</t>
         </is>
       </c>
-      <c r="C465" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D465" s="4" t="inlineStr"/>
-      <c r="E465" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F465" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>LG Washer User Control and Display Board - EBR78538807</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>newegg.com (fits WT7200CV/WT7200CW; board EAX65651804)</t>
         </is>
       </c>
     </row>
     <row r="466">
-      <c r="A466" s="4" t="inlineStr">
+      <c r="A466" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/3920dd3002a</t>
         </is>
       </c>
-      <c r="B466" s="4" t="inlineStr">
+      <c r="B466" t="inlineStr">
         <is>
           <t>3920dd3002a</t>
         </is>
       </c>
-      <c r="C466" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D466" s="4" t="inlineStr"/>
-      <c r="E466" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F466" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>LG Dishwasher Door Packing Seal - 3920DD3002A</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>lgparts.com dishwasher packing; searspartsdirect: replaced by 3920DD3002B</t>
         </is>
       </c>
     </row>
     <row r="467">
-      <c r="A467" s="4" t="inlineStr">
+      <c r="A467" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/mea62791001</t>
         </is>
       </c>
-      <c r="B467" s="4" t="inlineStr">
+      <c r="B467" t="inlineStr">
         <is>
           <t>mea62791001</t>
         </is>
       </c>
-      <c r="C467" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D467" s="4" t="inlineStr"/>
-      <c r="E467" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F467" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>LG Dryer Guide Cover - MEA62791001</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>lgparts.com (fr) dryer-parts collection Couvercle de guide de seche-linge</t>
         </is>
       </c>
     </row>
     <row r="468">
-      <c r="A468" s="4" t="inlineStr">
+      <c r="A468" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/agb73912401</t>
         </is>
       </c>
-      <c r="B468" s="4" t="inlineStr">
+      <c r="B468" t="inlineStr">
         <is>
           <t>agb73912401</t>
         </is>
       </c>
-      <c r="C468" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D468" s="4" t="inlineStr"/>
-      <c r="E468" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F468" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>LG Dishwasher Spray Nozzle Assembly - AGB73912401</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>lgparts.com (sprinkler nozzle), partswarehouse.com (nozzle assembly)</t>
         </is>
       </c>
     </row>
@@ -15049,30 +15451,34 @@
       </c>
     </row>
     <row r="470">
-      <c r="A470" s="4" t="inlineStr">
+      <c r="A470" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/4781w1a273t</t>
         </is>
       </c>
-      <c r="B470" s="4" t="inlineStr">
+      <c r="B470" t="inlineStr">
         <is>
           <t>4781w1a273t</t>
         </is>
       </c>
-      <c r="C470" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D470" s="4" t="inlineStr"/>
-      <c r="E470" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F470" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>LG Microwave Sub Controller Assembly - 4781W1A273T</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>lgparts.com microwave sub controller assembly</t>
         </is>
       </c>
     </row>
@@ -15237,86 +15643,98 @@
       </c>
     </row>
     <row r="476">
-      <c r="A476" s="4" t="inlineStr">
+      <c r="A476" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/5845ea1003b</t>
         </is>
       </c>
-      <c r="B476" s="4" t="inlineStr">
+      <c r="B476" t="inlineStr">
         <is>
           <t>5845ea1003b</t>
         </is>
       </c>
-      <c r="C476" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D476" s="4" t="inlineStr"/>
-      <c r="E476" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F476" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>LG Washer Pulsator Wash Plate - 5845EA1003B</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>lgparts.com LG Washer Wash plate Pulsator; newegg.com pulsator assembly</t>
         </is>
       </c>
     </row>
     <row r="477">
-      <c r="A477" s="4" t="inlineStr">
+      <c r="A477" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/6877el1007a</t>
         </is>
       </c>
-      <c r="B477" s="4" t="inlineStr">
+      <c r="B477" t="inlineStr">
         <is>
           <t>6877el1007a</t>
         </is>
       </c>
-      <c r="C477" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D477" s="4" t="inlineStr"/>
-      <c r="E477" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F477" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>LG Dryer Multi Wire Harness with Terminal Block - 6877EL1007A</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>lgparts.com (dryer parts collection)</t>
         </is>
       </c>
     </row>
     <row r="478">
-      <c r="A478" s="4" t="inlineStr">
+      <c r="A478" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/aeq73570501</t>
         </is>
       </c>
-      <c r="B478" s="4" t="inlineStr">
+      <c r="B478" t="inlineStr">
         <is>
           <t>aeq73570501</t>
         </is>
       </c>
-      <c r="C478" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D478" s="4" t="inlineStr"/>
-      <c r="E478" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F478" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Ice Maker Kit - AEQ73570501</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>lgparts.com ice maker kit/assembly</t>
         </is>
       </c>
     </row>
@@ -15513,142 +15931,162 @@
       </c>
     </row>
     <row r="485">
-      <c r="A485" s="4" t="inlineStr">
+      <c r="A485" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/ebg61486614</t>
         </is>
       </c>
-      <c r="B485" s="4" t="inlineStr">
+      <c r="B485" s="3" t="inlineStr">
         <is>
           <t>ebg61486614</t>
         </is>
       </c>
-      <c r="C485" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D485" s="4" t="inlineStr"/>
-      <c r="E485" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F485" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C485" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D485" s="3" t="inlineStr">
+        <is>
+          <t>LG Refrigerator PTC Thermistor Assembly - EBG61486614</t>
+        </is>
+      </c>
+      <c r="E485" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F485" s="3" t="inlineStr">
+        <is>
+          <t>exact number not found; sibling EBG61486617 is refrigerator PTC thermistor assembly (ebay.com, ifixit.com)</t>
         </is>
       </c>
     </row>
     <row r="486">
-      <c r="A486" s="4" t="inlineStr">
+      <c r="A486" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/man38143001</t>
         </is>
       </c>
-      <c r="B486" s="4" t="inlineStr">
+      <c r="B486" t="inlineStr">
         <is>
           <t>man38143001</t>
         </is>
       </c>
-      <c r="C486" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D486" s="4" t="inlineStr"/>
-      <c r="E486" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F486" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Window Door Basket - MAN38143001</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>hnkparts.com (basket window; fits LFX/LFC models)</t>
         </is>
       </c>
     </row>
     <row r="487">
-      <c r="A487" s="4" t="inlineStr">
+      <c r="A487" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/ebr85194701</t>
         </is>
       </c>
-      <c r="B487" s="4" t="inlineStr">
+      <c r="B487" t="inlineStr">
         <is>
           <t>ebr85194701</t>
         </is>
       </c>
-      <c r="C487" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D487" s="4" t="inlineStr"/>
-      <c r="E487" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F487" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>LG Washer Display Board Assembly - EBR85194701</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>newegg.com washer display PCB (WM3500CW)</t>
         </is>
       </c>
     </row>
     <row r="488">
-      <c r="A488" s="4" t="inlineStr">
+      <c r="A488" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/4890w1n005q</t>
         </is>
       </c>
-      <c r="B488" s="4" t="inlineStr">
+      <c r="B488" t="inlineStr">
         <is>
           <t>4890w1n005q</t>
         </is>
       </c>
-      <c r="C488" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D488" s="4" t="inlineStr"/>
-      <c r="E488" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F488" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>LG Range Oven Door Inner Glass - 4890W1N005Q</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>lgparts.com LG Range Oven Door Inner Glass</t>
         </is>
       </c>
     </row>
     <row r="489">
-      <c r="A489" s="4" t="inlineStr">
+      <c r="A489" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/5859er1002b</t>
         </is>
       </c>
-      <c r="B489" s="4" t="inlineStr">
+      <c r="B489" t="inlineStr">
         <is>
           <t>5859er1002b</t>
         </is>
       </c>
-      <c r="C489" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D489" s="4" t="inlineStr"/>
-      <c r="E489" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F489" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>LG Washer Drain Pump Assembly - 5859ER1002B</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>lgparts.com; variants 5859ER1002M/C elsewhere</t>
         </is>
       </c>
     </row>
@@ -15717,30 +16155,34 @@
       </c>
     </row>
     <row r="492">
-      <c r="A492" s="4" t="inlineStr">
+      <c r="A492" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/aeb73865905</t>
         </is>
       </c>
-      <c r="B492" s="4" t="inlineStr">
+      <c r="B492" t="inlineStr">
         <is>
           <t>aeb73865905</t>
         </is>
       </c>
-      <c r="C492" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D492" s="4" t="inlineStr"/>
-      <c r="E492" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F492" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Freezer Evaporator Cover and Fan Assembly - AEB73865905</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>lgparts.com</t>
         </is>
       </c>
     </row>
@@ -15809,30 +16251,34 @@
       </c>
     </row>
     <row r="495">
-      <c r="A495" s="4" t="inlineStr">
+      <c r="A495" s="2" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/cov34113801</t>
         </is>
       </c>
-      <c r="B495" s="4" t="inlineStr">
+      <c r="B495" s="2" t="inlineStr">
         <is>
           <t>cov34113801</t>
         </is>
       </c>
-      <c r="C495" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D495" s="4" t="inlineStr"/>
-      <c r="E495" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F495" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C495" s="2" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D495" s="2" t="inlineStr">
+        <is>
+          <t>LG Television Right Stand Base Leg - COV34113801</t>
+        </is>
+      </c>
+      <c r="E495" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F495" s="2" t="inlineStr">
+        <is>
+          <t>lgparts.com Base Leg (right); appliance not stated, TV stand inferred</t>
         </is>
       </c>
     </row>
@@ -15869,30 +16315,34 @@
       </c>
     </row>
     <row r="497">
-      <c r="A497" s="4" t="inlineStr">
+      <c r="A497" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/4779ja3001e</t>
         </is>
       </c>
-      <c r="B497" s="4" t="inlineStr">
+      <c r="B497" t="inlineStr">
         <is>
           <t>4779ja3001e</t>
         </is>
       </c>
-      <c r="C497" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D497" s="4" t="inlineStr"/>
-      <c r="E497" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F497" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Adjustable Leg Assembly - 4779JA3001E</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>partadvantage.com; siblings 4779JA3001K/H adjustable leg assemblies on lgparts.com</t>
         </is>
       </c>
     </row>
@@ -15929,142 +16379,162 @@
       </c>
     </row>
     <row r="499">
-      <c r="A499" s="4" t="inlineStr">
+      <c r="A499" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/aan30049802</t>
         </is>
       </c>
-      <c r="B499" s="4" t="inlineStr">
+      <c r="B499" s="3" t="inlineStr">
         <is>
           <t>aan30049802</t>
         </is>
       </c>
-      <c r="C499" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D499" s="4" t="inlineStr"/>
-      <c r="E499" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F499" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C499" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D499" s="3" t="inlineStr">
+        <is>
+          <t>LG Television Base Assembly - AAN30049802</t>
+        </is>
+      </c>
+      <c r="E499" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F499" s="3" t="inlineStr">
+        <is>
+          <t>lgparts.com base assembly exact; appliance not stated, TV guessed from AAN base prefix</t>
         </is>
       </c>
     </row>
     <row r="500">
-      <c r="A500" s="4" t="inlineStr">
+      <c r="A500" s="2" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/aju73432808</t>
         </is>
       </c>
-      <c r="B500" s="4" t="inlineStr">
+      <c r="B500" s="2" t="inlineStr">
         <is>
           <t>aju73432808</t>
         </is>
       </c>
-      <c r="C500" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D500" s="4" t="inlineStr"/>
-      <c r="E500" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F500" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C500" s="2" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D500" s="2" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Water Valve Assembly - AJU73432808</t>
+        </is>
+      </c>
+      <c r="E500" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F500" s="2" t="inlineStr">
+        <is>
+          <t>lgparts.com, genuinereplacementparts.com water valve assembly; appliance inferred from AJU734328xx refrigerator siblings (lgparts.com, shopjimmy.com)</t>
         </is>
       </c>
     </row>
     <row r="501">
-      <c r="A501" s="4" t="inlineStr">
+      <c r="A501" s="2" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/383ew1n006s</t>
         </is>
       </c>
-      <c r="B501" s="4" t="inlineStr">
+      <c r="B501" s="2" t="inlineStr">
         <is>
           <t>383ew1n006s</t>
         </is>
       </c>
-      <c r="C501" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D501" s="4" t="inlineStr"/>
-      <c r="E501" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F501" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C501" s="2" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D501" s="2" t="inlineStr">
+        <is>
+          <t>LG Range Control Panel and Cooktop Support Assembly - 383EW1N006S</t>
+        </is>
+      </c>
+      <c r="E501" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F501" s="2" t="inlineStr">
+        <is>
+          <t>lgparts.com lists only as parts assembly; siblings 383EW1N006L (keyboard/cooktop support, range), 383EW1N006N/F (range touch control panel)</t>
         </is>
       </c>
     </row>
     <row r="502">
-      <c r="A502" s="4" t="inlineStr">
+      <c r="A502" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/aju73753101</t>
         </is>
       </c>
-      <c r="B502" s="4" t="inlineStr">
+      <c r="B502" t="inlineStr">
         <is>
           <t>aju73753101</t>
         </is>
       </c>
-      <c r="C502" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D502" s="4" t="inlineStr"/>
-      <c r="E502" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F502" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Water Inlet Valve Assembly - AJU73753101</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>lgparts.com, hnkparts, ifixit; replaces MJU62186801</t>
         </is>
       </c>
     </row>
     <row r="503">
-      <c r="A503" s="4" t="inlineStr">
+      <c r="A503" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/agm74189101</t>
         </is>
       </c>
-      <c r="B503" s="4" t="inlineStr">
+      <c r="B503" t="inlineStr">
         <is>
           <t>agm74189101</t>
         </is>
       </c>
-      <c r="C503" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D503" s="4" t="inlineStr"/>
-      <c r="E503" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F503" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>LG Washer Wash Pump Motor - AGM74189101</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>lgparts.com wash pump motor pages for WM4070HVA/WM4070HWA</t>
         </is>
       </c>
     </row>
@@ -16101,86 +16571,98 @@
       </c>
     </row>
     <row r="505">
-      <c r="A505" s="4" t="inlineStr">
+      <c r="A505" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/ebr89076002</t>
         </is>
       </c>
-      <c r="B505" s="4" t="inlineStr">
+      <c r="B505" s="3" t="inlineStr">
         <is>
           <t>ebr89076002</t>
         </is>
       </c>
-      <c r="C505" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D505" s="4" t="inlineStr"/>
-      <c r="E505" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F505" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C505" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D505" s="3" t="inlineStr">
+        <is>
+          <t>LG Washer Display Power Control Board - EBR89076002</t>
+        </is>
+      </c>
+      <c r="E505" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F505" s="3" t="inlineStr">
+        <is>
+          <t>exact number not found; siblings EBR89076001 (washer display power control board), EBR89076006 (user interface board)</t>
         </is>
       </c>
     </row>
     <row r="506">
-      <c r="A506" s="4" t="inlineStr">
+      <c r="A506" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/acq85626204</t>
         </is>
       </c>
-      <c r="B506" s="4" t="inlineStr">
+      <c r="B506" s="3" t="inlineStr">
         <is>
           <t>acq85626204</t>
         </is>
       </c>
-      <c r="C506" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D506" s="4" t="inlineStr"/>
-      <c r="E506" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F506" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C506" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D506" s="3" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Cover Assembly - ACQ85626204</t>
+        </is>
+      </c>
+      <c r="E506" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F506" s="3" t="inlineStr">
+        <is>
+          <t>exact not found; ACQ siblings are refrigerator covers (lgparts, ersatzteilshop.de); guess</t>
         </is>
       </c>
     </row>
     <row r="507">
-      <c r="A507" s="4" t="inlineStr">
+      <c r="A507" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/cov33552433</t>
         </is>
       </c>
-      <c r="B507" s="4" t="inlineStr">
+      <c r="B507" s="3" t="inlineStr">
         <is>
           <t>cov33552433</t>
         </is>
       </c>
-      <c r="C507" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D507" s="4" t="inlineStr"/>
-      <c r="E507" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F507" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C507" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D507" s="3" t="inlineStr">
+        <is>
+          <t>LG Sound Bar Remote Control - COV33552433</t>
+        </is>
+      </c>
+      <c r="E507" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F507" s="3" t="inlineStr">
+        <is>
+          <t>exact number not found; siblings COV33552438 (soundbar remote, lgparts.com) and COV33552428 (remote controller)</t>
         </is>
       </c>
     </row>
@@ -16217,58 +16699,66 @@
       </c>
     </row>
     <row r="509">
-      <c r="A509" s="4" t="inlineStr">
+      <c r="A509" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/5988ja1001e</t>
         </is>
       </c>
-      <c r="B509" s="4" t="inlineStr">
+      <c r="B509" t="inlineStr">
         <is>
           <t>5988ja1001e</t>
         </is>
       </c>
-      <c r="C509" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D509" s="4" t="inlineStr"/>
-      <c r="E509" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F509" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Ice Maker Control Module - 5988JA1001E</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>lgparts.com, spareka.fr (ice maker control unit)</t>
         </is>
       </c>
     </row>
     <row r="510">
-      <c r="A510" s="4" t="inlineStr">
+      <c r="A510" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/akb76038002</t>
         </is>
       </c>
-      <c r="B510" s="4" t="inlineStr">
+      <c r="B510" s="3" t="inlineStr">
         <is>
           <t>akb76038002</t>
         </is>
       </c>
-      <c r="C510" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D510" s="4" t="inlineStr"/>
-      <c r="E510" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F510" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C510" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D510" s="3" t="inlineStr">
+        <is>
+          <t>LG Sound Bar Remote Control - AKB76038002</t>
+        </is>
+      </c>
+      <c r="E510" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F510" s="3" t="inlineStr">
+        <is>
+          <t>exact not found; sibling AKB76038001 sound bar remote (shopjimmy, ebay)</t>
         </is>
       </c>
     </row>
@@ -16401,58 +16891,66 @@
       </c>
     </row>
     <row r="515">
-      <c r="A515" s="4" t="inlineStr">
+      <c r="A515" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/ajp73314412</t>
         </is>
       </c>
-      <c r="B515" s="4" t="inlineStr">
+      <c r="B515" s="3" t="inlineStr">
         <is>
           <t>ajp73314412</t>
         </is>
       </c>
-      <c r="C515" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D515" s="4" t="inlineStr"/>
-      <c r="E515" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F515" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C515" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D515" s="3" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Fresh Room Tray Assembly - AJP73314412</t>
+        </is>
+      </c>
+      <c r="E515" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F515" s="3" t="inlineStr">
+        <is>
+          <t>exact number not found; siblings AJP73314421/AJP73314427 are refrigerator fresh room/deli drawer trays (lgparts.com, newegg.com)</t>
         </is>
       </c>
     </row>
     <row r="516">
-      <c r="A516" s="4" t="inlineStr">
+      <c r="A516" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/5075jj1003a</t>
         </is>
       </c>
-      <c r="B516" s="4" t="inlineStr">
+      <c r="B516" t="inlineStr">
         <is>
           <t>5075jj1003a</t>
         </is>
       </c>
-      <c r="C516" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D516" s="4" t="inlineStr"/>
-      <c r="E516" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F516" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Ice Bucket Assembly - 5075JJ1003A</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>lgparts.com (freezer ice bin, clear with white trim)</t>
         </is>
       </c>
     </row>
@@ -16489,30 +16987,34 @@
       </c>
     </row>
     <row r="518">
-      <c r="A518" s="4" t="inlineStr">
+      <c r="A518" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/ebr79523102</t>
         </is>
       </c>
-      <c r="B518" s="4" t="inlineStr">
+      <c r="B518" t="inlineStr">
         <is>
           <t>ebr79523102</t>
         </is>
       </c>
-      <c r="C518" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D518" s="4" t="inlineStr"/>
-      <c r="E518" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F518" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>LG Washer Display Board Assembly - EBR79523102</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>newegg.com washer display/control board; alt EBR79559801</t>
         </is>
       </c>
     </row>
@@ -16549,58 +17051,66 @@
       </c>
     </row>
     <row r="520">
-      <c r="A520" s="4" t="inlineStr">
+      <c r="A520" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/eaf36358316</t>
         </is>
       </c>
-      <c r="B520" s="4" t="inlineStr">
+      <c r="B520" s="3" t="inlineStr">
         <is>
           <t>eaf36358316</t>
         </is>
       </c>
-      <c r="C520" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D520" s="4" t="inlineStr"/>
-      <c r="E520" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F520" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C520" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D520" s="3" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Fuse Assembly - EAF36358316</t>
+        </is>
+      </c>
+      <c r="E520" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F520" s="3" t="inlineStr">
+        <is>
+          <t>exact number not found; siblings EAF36358317/314 are fuse assemblies (lgparts.com); appliance guessed</t>
         </is>
       </c>
     </row>
     <row r="521">
-      <c r="A521" s="4" t="inlineStr">
+      <c r="A521" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/5220fr2075p</t>
         </is>
       </c>
-      <c r="B521" s="4" t="inlineStr">
+      <c r="B521" t="inlineStr">
         <is>
           <t>5220fr2075p</t>
         </is>
       </c>
-      <c r="C521" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D521" s="4" t="inlineStr"/>
-      <c r="E521" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F521" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>LG Washer Water Inlet Valve Assembly - 5220FR2075P</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>lgparts.com; variants 5220FR2075L/V elsewhere</t>
         </is>
       </c>
     </row>
@@ -16637,114 +17147,130 @@
       </c>
     </row>
     <row r="523">
-      <c r="A523" s="4" t="inlineStr">
+      <c r="A523" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/4775er2002e</t>
         </is>
       </c>
-      <c r="B523" s="4" t="inlineStr">
+      <c r="B523" t="inlineStr">
         <is>
           <t>4775er2002e</t>
         </is>
       </c>
-      <c r="C523" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D523" s="4" t="inlineStr"/>
-      <c r="E523" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F523" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>LG Washer Hinge Assembly - 4775ER2002E</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>lgparts.com washer hinge (fr)</t>
         </is>
       </c>
     </row>
     <row r="524">
-      <c r="A524" s="4" t="inlineStr">
+      <c r="A524" s="2" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/agl75452910</t>
         </is>
       </c>
-      <c r="B524" s="4" t="inlineStr">
+      <c r="B524" s="2" t="inlineStr">
         <is>
           <t>agl75452910</t>
         </is>
       </c>
-      <c r="C524" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D524" s="4" t="inlineStr"/>
-      <c r="E524" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F524" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C524" s="2" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D524" s="2" t="inlineStr">
+        <is>
+          <t>LG Washer Front Panel Assembly - AGL75452910</t>
+        </is>
+      </c>
+      <c r="E524" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F524" s="2" t="inlineStr">
+        <is>
+          <t>lgparts.com Front Panel Assembly; appliance inferred: sibling AGL75452911 washer front panel (ereplacementparts.com), AGL75452921 dryer</t>
         </is>
       </c>
     </row>
     <row r="525">
-      <c r="A525" s="4" t="inlineStr">
+      <c r="A525" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/aju74852802</t>
         </is>
       </c>
-      <c r="B525" s="4" t="inlineStr">
+      <c r="B525" t="inlineStr">
         <is>
           <t>aju74852802</t>
         </is>
       </c>
-      <c r="C525" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D525" s="4" t="inlineStr"/>
-      <c r="E525" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F525" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>LG Range Gas Valve Assembly - AJU74852802</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>lgparts.com (range collection), genuinereplacementparts.com; replaces MJX61842211</t>
         </is>
       </c>
     </row>
     <row r="526">
-      <c r="A526" s="4" t="inlineStr">
+      <c r="A526" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/aez73913405</t>
         </is>
       </c>
-      <c r="B526" s="4" t="inlineStr">
+      <c r="B526" t="inlineStr">
         <is>
           <t>aez73913405</t>
         </is>
       </c>
-      <c r="C526" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D526" s="4" t="inlineStr"/>
-      <c r="E526" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F526" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>LG Dryer Knob Assembly - AEZ73913405</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>lgparts.com Dryer Knob; ifixit titles it oven knob but lists dryer/washer models</t>
         </is>
       </c>
     </row>
@@ -16813,114 +17339,130 @@
       </c>
     </row>
     <row r="529">
-      <c r="A529" s="4" t="inlineStr">
+      <c r="A529" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/agm75469905</t>
         </is>
       </c>
-      <c r="B529" s="4" t="inlineStr">
+      <c r="B529" s="3" t="inlineStr">
         <is>
           <t>agm75469905</t>
         </is>
       </c>
-      <c r="C529" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D529" s="4" t="inlineStr"/>
-      <c r="E529" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F529" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C529" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D529" s="3" t="inlineStr">
+        <is>
+          <t>LG Dishwasher Control Panel Assembly - AGM75469905</t>
+        </is>
+      </c>
+      <c r="E529" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F529" s="3" t="inlineStr">
+        <is>
+          <t>exact number not found; siblings AGM75469908/902/910 are dishwasher parts/control panel assemblies (lgparts.com, ifixit.com, ebay.com)</t>
         </is>
       </c>
     </row>
     <row r="530">
-      <c r="A530" s="4" t="inlineStr">
+      <c r="A530" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/ebr85194702</t>
         </is>
       </c>
-      <c r="B530" s="4" t="inlineStr">
+      <c r="B530" t="inlineStr">
         <is>
           <t>ebr85194702</t>
         </is>
       </c>
-      <c r="C530" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D530" s="4" t="inlineStr"/>
-      <c r="E530" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F530" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>LG Washer Display PCB Assembly - EBR85194702</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>ereplacementparts.com, newegg.com (fits WM3700HRA/HVA/HWA); discontinued</t>
         </is>
       </c>
     </row>
     <row r="531">
-      <c r="A531" s="4" t="inlineStr">
+      <c r="A531" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/agl36868103</t>
         </is>
       </c>
-      <c r="B531" s="4" t="inlineStr">
+      <c r="B531" t="inlineStr">
         <is>
           <t>agl36868103</t>
         </is>
       </c>
-      <c r="C531" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D531" s="4" t="inlineStr"/>
-      <c r="E531" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F531" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>LG Dishwasher Control Panel Assembly - AGL36868103</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>lgparts.com dishwasher control panel; genuinereplacementparts.com chrome UI panel</t>
         </is>
       </c>
     </row>
     <row r="532">
-      <c r="A532" s="4" t="inlineStr">
+      <c r="A532" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/akb73896401</t>
         </is>
       </c>
-      <c r="B532" s="4" t="inlineStr">
+      <c r="B532" t="inlineStr">
         <is>
           <t>akb73896401</t>
         </is>
       </c>
-      <c r="C532" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D532" s="4" t="inlineStr"/>
-      <c r="E532" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F532" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>LG Blu-ray Player Remote Control - AKB73896401</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>walmart.com, av-connection.com; fits BP135, BP145, BP155, BP175, BP255, BP300, BP335W, BP340, BP350</t>
         </is>
       </c>
     </row>
@@ -16989,142 +17531,162 @@
       </c>
     </row>
     <row r="535">
-      <c r="A535" s="4" t="inlineStr">
+      <c r="A535" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/cov33315901</t>
         </is>
       </c>
-      <c r="B535" s="4" t="inlineStr">
+      <c r="B535" t="inlineStr">
         <is>
           <t>cov33315901</t>
         </is>
       </c>
-      <c r="C535" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D535" s="4" t="inlineStr"/>
-      <c r="E535" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F535" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>LG Air Conditioner Window Panel with Oval Hole - COV33315901</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>lgparts.com (portable air conditioner window panel); siblings COV33315201 exhaust hose</t>
         </is>
       </c>
     </row>
     <row r="536">
-      <c r="A536" s="4" t="inlineStr">
+      <c r="A536" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/aan30028920</t>
         </is>
       </c>
-      <c r="B536" s="4" t="inlineStr">
+      <c r="B536" s="3" t="inlineStr">
         <is>
           <t>aan30028920</t>
         </is>
       </c>
-      <c r="C536" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D536" s="4" t="inlineStr"/>
-      <c r="E536" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F536" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C536" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D536" s="3" t="inlineStr">
+        <is>
+          <t>LG Television Base Assembly - AAN30028920</t>
+        </is>
+      </c>
+      <c r="E536" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F536" s="3" t="inlineStr">
+        <is>
+          <t>exact not found; siblings AAN30028921/40 base (lgparts); TV guessed</t>
         </is>
       </c>
     </row>
     <row r="537">
-      <c r="A537" s="4" t="inlineStr">
+      <c r="A537" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/agm73830201</t>
         </is>
       </c>
-      <c r="B537" s="4" t="inlineStr">
+      <c r="B537" s="3" t="inlineStr">
         <is>
           <t>agm73830201</t>
         </is>
       </c>
-      <c r="C537" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D537" s="4" t="inlineStr"/>
-      <c r="E537" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F537" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C537" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D537" s="3" t="inlineStr">
+        <is>
+          <t>LG Range Parts Assembly - AGM73830201</t>
+        </is>
+      </c>
+      <c r="E537" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F537" s="3" t="inlineStr">
+        <is>
+          <t>exact number not found; sibling AGM73830202 LG Range Parts assembly (lgparts.com)</t>
         </is>
       </c>
     </row>
     <row r="538">
-      <c r="A538" s="4" t="inlineStr">
+      <c r="A538" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/ebr62707645</t>
         </is>
       </c>
-      <c r="B538" s="4" t="inlineStr">
+      <c r="B538" t="inlineStr">
         <is>
           <t>ebr62707645</t>
         </is>
       </c>
-      <c r="C538" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D538" s="4" t="inlineStr"/>
-      <c r="E538" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F538" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>LG Dryer Main Control Board - EBR62707645</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>lgparts.com (dryer collection; fits DLEX3070W/DLEX3470W), newegg.com</t>
         </is>
       </c>
     </row>
     <row r="539">
-      <c r="A539" s="4" t="inlineStr">
+      <c r="A539" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/ead61273132</t>
         </is>
       </c>
-      <c r="B539" s="4" t="inlineStr">
+      <c r="B539" s="3" t="inlineStr">
         <is>
           <t>ead61273132</t>
         </is>
       </c>
-      <c r="C539" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D539" s="4" t="inlineStr"/>
-      <c r="E539" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F539" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C539" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D539" s="3" t="inlineStr">
+        <is>
+          <t>LG Television Cable Assembly - EAD61273132</t>
+        </is>
+      </c>
+      <c r="E539" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F539" s="3" t="inlineStr">
+        <is>
+          <t>exact not found; sibling EAD61273113 TV stereo plug cable (lgparts)</t>
         </is>
       </c>
     </row>
@@ -17161,86 +17723,98 @@
       </c>
     </row>
     <row r="541">
-      <c r="A541" s="4" t="inlineStr">
+      <c r="A541" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/acj74110101</t>
         </is>
       </c>
-      <c r="B541" s="4" t="inlineStr">
+      <c r="B541" s="3" t="inlineStr">
         <is>
           <t>acj74110101</t>
         </is>
       </c>
-      <c r="C541" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D541" s="4" t="inlineStr"/>
-      <c r="E541" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F541" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C541" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D541" s="3" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Connector Assembly - ACJ74110101</t>
+        </is>
+      </c>
+      <c r="E541" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F541" s="3" t="inlineStr">
+        <is>
+          <t>lgparts.com Connector Assembly; appliance not stated, refrigerator guessed</t>
         </is>
       </c>
     </row>
     <row r="542">
-      <c r="A542" s="4" t="inlineStr">
+      <c r="A542" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/aeq73449911</t>
         </is>
       </c>
-      <c r="B542" s="4" t="inlineStr">
+      <c r="B542" t="inlineStr">
         <is>
           <t>aeq73449911</t>
         </is>
       </c>
-      <c r="C542" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D542" s="4" t="inlineStr"/>
-      <c r="E542" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F542" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Ice Maker Kit - AEQ73449911</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>lgparts.com (refrigerator parts collection); siblings AEQ73449909/12/13</t>
         </is>
       </c>
     </row>
     <row r="543">
-      <c r="A543" s="4" t="inlineStr">
+      <c r="A543" s="2" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/ebr85624973</t>
         </is>
       </c>
-      <c r="B543" s="4" t="inlineStr">
+      <c r="B543" s="2" t="inlineStr">
         <is>
           <t>ebr85624973</t>
         </is>
       </c>
-      <c r="C543" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D543" s="4" t="inlineStr"/>
-      <c r="E543" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F543" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C543" s="2" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D543" s="2" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Main Control Board - EBR85624973</t>
+        </is>
+      </c>
+      <c r="E543" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F543" s="2" t="inlineStr">
+        <is>
+          <t>lgparts.com refrigerator-parts collection main PCB; sibling EBR85624977 is a washer board (conflict)</t>
         </is>
       </c>
     </row>
@@ -17373,30 +17947,34 @@
       </c>
     </row>
     <row r="548">
-      <c r="A548" s="4" t="inlineStr">
+      <c r="A548" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/ebr39528803</t>
         </is>
       </c>
-      <c r="B548" s="4" t="inlineStr">
+      <c r="B548" s="3" t="inlineStr">
         <is>
           <t>ebr39528803</t>
         </is>
       </c>
-      <c r="C548" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D548" s="4" t="inlineStr"/>
-      <c r="E548" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F548" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C548" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D548" s="3" t="inlineStr">
+        <is>
+          <t>LG Dryer Main Control Board - EBR39528803</t>
+        </is>
+      </c>
+      <c r="E548" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F548" s="3" t="inlineStr">
+        <is>
+          <t>exact number not found; siblings EBR39528802/805 are dryer control boards for DLG7001W, DLE3400W (shopjimmy.com)</t>
         </is>
       </c>
     </row>
@@ -17529,58 +18107,66 @@
       </c>
     </row>
     <row r="553">
-      <c r="A553" s="4" t="inlineStr">
+      <c r="A553" s="2" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/maz67575013</t>
         </is>
       </c>
-      <c r="B553" s="4" t="inlineStr">
+      <c r="B553" s="2" t="inlineStr">
         <is>
           <t>maz67575013</t>
         </is>
       </c>
-      <c r="C553" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D553" s="4" t="inlineStr"/>
-      <c r="E553" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F553" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C553" s="2" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D553" s="2" t="inlineStr">
+        <is>
+          <t>LG Television Stand Support Bracket - MAZ67575013</t>
+        </is>
+      </c>
+      <c r="E553" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F553" s="2" t="inlineStr">
+        <is>
+          <t>lgparts.com French page lists as television support; no model list</t>
         </is>
       </c>
     </row>
     <row r="554">
-      <c r="A554" s="4" t="inlineStr">
+      <c r="A554" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/aeb72913929</t>
         </is>
       </c>
-      <c r="B554" s="4" t="inlineStr">
+      <c r="B554" t="inlineStr">
         <is>
           <t>aeb72913929</t>
         </is>
       </c>
-      <c r="C554" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D554" s="4" t="inlineStr"/>
-      <c r="E554" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F554" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Freezer Fan and Grille Assembly - AEB72913929</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>lgparts.com, walmart, hdsupply, newegg; replaces AEB72913924</t>
         </is>
       </c>
     </row>
@@ -17649,30 +18235,34 @@
       </c>
     </row>
     <row r="557">
-      <c r="A557" s="4" t="inlineStr">
+      <c r="A557" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/agl76992504</t>
         </is>
       </c>
-      <c r="B557" s="4" t="inlineStr">
+      <c r="B557" s="3" t="inlineStr">
         <is>
           <t>agl76992504</t>
         </is>
       </c>
-      <c r="C557" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D557" s="4" t="inlineStr"/>
-      <c r="E557" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F557" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C557" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D557" s="3" t="inlineStr">
+        <is>
+          <t>LG Dryer Control Panel Assembly - AGL76992504</t>
+        </is>
+      </c>
+      <c r="E557" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F557" s="3" t="inlineStr">
+        <is>
+          <t>exact number not found; siblings AGL76992503/502/518 are dryer control panel assemblies (lgparts.com, ebay.de)</t>
         </is>
       </c>
     </row>
@@ -17709,30 +18299,34 @@
       </c>
     </row>
     <row r="559">
-      <c r="A559" s="4" t="inlineStr">
+      <c r="A559" s="2" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/adc73927703</t>
         </is>
       </c>
-      <c r="B559" s="4" t="inlineStr">
+      <c r="B559" s="2" t="inlineStr">
         <is>
           <t>adc73927703</t>
         </is>
       </c>
-      <c r="C559" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D559" s="4" t="inlineStr"/>
-      <c r="E559" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F559" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C559" s="2" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D559" s="2" t="inlineStr">
+        <is>
+          <t>LG Dryer Door Assembly - ADC73927703</t>
+        </is>
+      </c>
+      <c r="E559" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F559" s="2" t="inlineStr">
+        <is>
+          <t>lgparts.com lists as door assembly; dryer per search summary/sibling ADC73927702 dryer door, but ADC73927704 is a washer door</t>
         </is>
       </c>
     </row>
@@ -17801,86 +18395,98 @@
       </c>
     </row>
     <row r="562">
-      <c r="A562" s="4" t="inlineStr">
+      <c r="A562" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/5249dd1001d</t>
         </is>
       </c>
-      <c r="B562" s="4" t="inlineStr">
+      <c r="B562" t="inlineStr">
         <is>
           <t>5249dd1001d</t>
         </is>
       </c>
-      <c r="C562" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D562" s="4" t="inlineStr"/>
-      <c r="E562" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F562" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>LG Dishwasher Nozzle Assembly - 5249DD1001D</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>lgparts.com</t>
         </is>
       </c>
     </row>
     <row r="563">
-      <c r="A563" s="4" t="inlineStr">
+      <c r="A563" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/man62429801</t>
         </is>
       </c>
-      <c r="B563" s="4" t="inlineStr">
+      <c r="B563" s="3" t="inlineStr">
         <is>
           <t>man62429801</t>
         </is>
       </c>
-      <c r="C563" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D563" s="4" t="inlineStr"/>
-      <c r="E563" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F563" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C563" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D563" s="3" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Door Basket - MAN62429801</t>
+        </is>
+      </c>
+      <c r="E563" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F563" s="3" t="inlineStr">
+        <is>
+          <t>exact number not found; MAN-series siblings are refrigerator door baskets/shelf guards (lgparts.com, ebay.de, appliancefactoryparts.com)</t>
         </is>
       </c>
     </row>
     <row r="564">
-      <c r="A564" s="4" t="inlineStr">
+      <c r="A564" s="2" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/4901jk1001b</t>
         </is>
       </c>
-      <c r="B564" s="4" t="inlineStr">
+      <c r="B564" s="2" t="inlineStr">
         <is>
           <t>4901jk1001b</t>
         </is>
       </c>
-      <c r="C564" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D564" s="4" t="inlineStr"/>
-      <c r="E564" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F564" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C564" s="2" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D564" s="2" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Motor Damper Assembly - 4901JK1001B</t>
+        </is>
+      </c>
+      <c r="E564" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F564" s="2" t="inlineStr">
+        <is>
+          <t>exact number not found; suffix sibling 4901JK1001K motor damper assembly on lgparts.com</t>
         </is>
       </c>
     </row>
@@ -17949,86 +18555,98 @@
       </c>
     </row>
     <row r="567">
-      <c r="A567" s="4" t="inlineStr">
+      <c r="A567" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/adx73350633</t>
         </is>
       </c>
-      <c r="B567" s="4" t="inlineStr">
+      <c r="B567" t="inlineStr">
         <is>
           <t>adx73350633</t>
         </is>
       </c>
-      <c r="C567" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D567" s="4" t="inlineStr"/>
-      <c r="E567" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F567" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Door Gasket Assembly - ADX73350633</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>lgparts.com, filtersfast.com</t>
         </is>
       </c>
     </row>
     <row r="568">
-      <c r="A568" s="4" t="inlineStr">
+      <c r="A568" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/agm30037301</t>
         </is>
       </c>
-      <c r="B568" s="4" t="inlineStr">
+      <c r="B568" t="inlineStr">
         <is>
           <t>agm30037301</t>
         </is>
       </c>
-      <c r="C568" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D568" s="4" t="inlineStr"/>
-      <c r="E568" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F568" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>LG Range Control Panel Assembly - AGM30037301</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>shopjimmy.com range control panel for LSEL6333F; lgparts.com range parts assembly</t>
         </is>
       </c>
     </row>
     <row r="569">
-      <c r="A569" s="4" t="inlineStr">
+      <c r="A569" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/3661ea1009e</t>
         </is>
       </c>
-      <c r="B569" s="4" t="inlineStr">
+      <c r="B569" t="inlineStr">
         <is>
           <t>3661ea1009e</t>
         </is>
       </c>
-      <c r="C569" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D569" s="4" t="inlineStr"/>
-      <c r="E569" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F569" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>LG Washer Clutch Coupling Housing Assembly - 3661EA1009E</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>lgparts.com; suffix sibling 3661EA1009D</t>
         </is>
       </c>
     </row>
@@ -18129,30 +18747,34 @@
       </c>
     </row>
     <row r="573">
-      <c r="A573" s="4" t="inlineStr">
+      <c r="A573" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/5221jb2010u</t>
         </is>
       </c>
-      <c r="B573" s="4" t="inlineStr">
+      <c r="B573" s="3" t="inlineStr">
         <is>
           <t>5221jb2010u</t>
         </is>
       </c>
-      <c r="C573" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D573" s="4" t="inlineStr"/>
-      <c r="E573" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F573" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C573" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D573" s="3" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Water Valve Assembly - 5221JB2010U</t>
+        </is>
+      </c>
+      <c r="E573" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F573" s="3" t="inlineStr">
+        <is>
+          <t>exact not found; sibling 5221JB2010E water valve assembly (lgparts); appliance guessed</t>
         </is>
       </c>
     </row>
@@ -18189,58 +18811,66 @@
       </c>
     </row>
     <row r="575">
-      <c r="A575" s="4" t="inlineStr">
+      <c r="A575" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/3551jj2034b</t>
         </is>
       </c>
-      <c r="B575" s="4" t="inlineStr">
+      <c r="B575" s="3" t="inlineStr">
         <is>
           <t>3551jj2034b</t>
         </is>
       </c>
-      <c r="C575" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D575" s="4" t="inlineStr"/>
-      <c r="E575" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F575" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C575" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D575" s="3" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Right Mullion Cover - 3551JJ2034B</t>
+        </is>
+      </c>
+      <c r="E575" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F575" s="3" t="inlineStr">
+        <is>
+          <t>exact number not found; siblings 3551JJ2034A (Refrigerator Mullion Right) and 3551JJ2034D (refrigerator front cover) on lgparts.com</t>
         </is>
       </c>
     </row>
     <row r="576">
-      <c r="A576" s="4" t="inlineStr">
+      <c r="A576" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/5027jq2006a</t>
         </is>
       </c>
-      <c r="B576" s="4" t="inlineStr">
+      <c r="B576" s="3" t="inlineStr">
         <is>
           <t>5027jq2006a</t>
         </is>
       </c>
-      <c r="C576" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D576" s="4" t="inlineStr"/>
-      <c r="E576" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F576" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C576" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D576" s="3" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Shelf Assembly - 5027JQ2006A</t>
+        </is>
+      </c>
+      <c r="E576" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F576" s="3" t="inlineStr">
+        <is>
+          <t>exact number not found; sibling 5027JQ2007A refrigerator shelf assembly on lgparts.com</t>
         </is>
       </c>
     </row>
@@ -18277,58 +18907,66 @@
       </c>
     </row>
     <row r="578">
-      <c r="A578" s="4" t="inlineStr">
+      <c r="A578" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/adc72922713</t>
         </is>
       </c>
-      <c r="B578" s="4" t="inlineStr">
+      <c r="B578" t="inlineStr">
         <is>
           <t>adc72922713</t>
         </is>
       </c>
-      <c r="C578" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D578" s="4" t="inlineStr"/>
-      <c r="E578" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F578" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>LG Dryer Door Assembly - ADC72922713</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>lgparts.com dryer door</t>
         </is>
       </c>
     </row>
     <row r="579">
-      <c r="A579" s="4" t="inlineStr">
+      <c r="A579" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/mck67662703</t>
         </is>
       </c>
-      <c r="B579" s="4" t="inlineStr">
+      <c r="B579" s="3" t="inlineStr">
         <is>
           <t>mck67662703</t>
         </is>
       </c>
-      <c r="C579" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D579" s="4" t="inlineStr"/>
-      <c r="E579" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F579" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C579" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D579" s="3" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Cover - MCK67662703</t>
+        </is>
+      </c>
+      <c r="E579" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F579" s="3" t="inlineStr">
+        <is>
+          <t>exact number not found; MCK-series are covers across refrigerator/washer; appliance guessed</t>
         </is>
       </c>
     </row>
@@ -18397,86 +19035,98 @@
       </c>
     </row>
     <row r="582">
-      <c r="A582" s="4" t="inlineStr">
+      <c r="A582" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/3721er1006r</t>
         </is>
       </c>
-      <c r="B582" s="4" t="inlineStr">
+      <c r="B582" t="inlineStr">
         <is>
           <t>3721er1006r</t>
         </is>
       </c>
-      <c r="C582" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D582" s="4" t="inlineStr"/>
-      <c r="E582" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F582" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>LG Washer Dispenser Drawer Panel - 3721ER1006R</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>lgparts.com (washer drawer panel); sibling 3721ER1006Z</t>
         </is>
       </c>
     </row>
     <row r="583">
-      <c r="A583" s="4" t="inlineStr">
+      <c r="A583" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/man62188301</t>
         </is>
       </c>
-      <c r="B583" s="4" t="inlineStr">
+      <c r="B583" s="3" t="inlineStr">
         <is>
           <t>man62188301</t>
         </is>
       </c>
-      <c r="C583" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D583" s="4" t="inlineStr"/>
-      <c r="E583" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F583" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C583" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D583" s="3" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Door Basket - MAN62188301</t>
+        </is>
+      </c>
+      <c r="E583" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F583" s="3" t="inlineStr">
+        <is>
+          <t>exact not found; MAN-prefix siblings are refrigerator door baskets</t>
         </is>
       </c>
     </row>
     <row r="584">
-      <c r="A584" s="4" t="inlineStr">
+      <c r="A584" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/ajp73474801</t>
         </is>
       </c>
-      <c r="B584" s="4" t="inlineStr">
+      <c r="B584" s="3" t="inlineStr">
         <is>
           <t>ajp73474801</t>
         </is>
       </c>
-      <c r="C584" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D584" s="4" t="inlineStr"/>
-      <c r="E584" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F584" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C584" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D584" s="3" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Tray Assembly - AJP73474801</t>
+        </is>
+      </c>
+      <c r="E584" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F584" s="3" t="inlineStr">
+        <is>
+          <t>exact number not found; only unrelated AJR73484701/801 inject tubes returned; AJP prefix is tray assembly, refrigerator guessed</t>
         </is>
       </c>
     </row>
@@ -18641,30 +19291,34 @@
       </c>
     </row>
     <row r="590">
-      <c r="A590" s="4" t="inlineStr">
+      <c r="A590" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/adc73025601</t>
         </is>
       </c>
-      <c r="B590" s="4" t="inlineStr">
+      <c r="B590" t="inlineStr">
         <is>
           <t>adc73025601</t>
         </is>
       </c>
-      <c r="C590" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D590" s="4" t="inlineStr"/>
-      <c r="E590" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F590" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>LG Dryer Door Assembly - ADC73025601</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>lgparts.com</t>
         </is>
       </c>
     </row>
@@ -18701,30 +19355,34 @@
       </c>
     </row>
     <row r="592">
-      <c r="A592" s="4" t="inlineStr">
+      <c r="A592" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/aeh72976204</t>
         </is>
       </c>
-      <c r="B592" s="4" t="inlineStr">
+      <c r="B592" t="inlineStr">
         <is>
           <t>aeh72976204</t>
         </is>
       </c>
-      <c r="C592" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D592" s="4" t="inlineStr"/>
-      <c r="E592" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F592" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Upper Hinge Assembly - AEH72976204</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>lgparts.com, genuinereplacementparts.com</t>
         </is>
       </c>
     </row>
@@ -18761,30 +19419,34 @@
       </c>
     </row>
     <row r="594">
-      <c r="A594" s="4" t="inlineStr">
+      <c r="A594" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/4775ja2113a</t>
         </is>
       </c>
-      <c r="B594" s="4" t="inlineStr">
+      <c r="B594" t="inlineStr">
         <is>
           <t>4775ja2113a</t>
         </is>
       </c>
-      <c r="C594" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D594" s="4" t="inlineStr"/>
-      <c r="E594" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F594" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Lower Door Hinge Assembly - 4775JA2113A</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>lgparts.com Refrigerator Door Hinge Assembly, Lower; filtersfast.com</t>
         </is>
       </c>
     </row>
@@ -18821,30 +19483,34 @@
       </c>
     </row>
     <row r="596">
-      <c r="A596" s="4" t="inlineStr">
+      <c r="A596" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/adc74154906</t>
         </is>
       </c>
-      <c r="B596" s="4" t="inlineStr">
+      <c r="B596" t="inlineStr">
         <is>
           <t>adc74154906</t>
         </is>
       </c>
-      <c r="C596" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D596" s="4" t="inlineStr"/>
-      <c r="E596" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F596" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>LG Washer Door Assembly - ADC74154906</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>lgparts.com, ebay (glass washer door, also ADC74154902)</t>
         </is>
       </c>
     </row>
@@ -18881,58 +19547,66 @@
       </c>
     </row>
     <row r="598">
-      <c r="A598" s="4" t="inlineStr">
+      <c r="A598" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/ebr85755504</t>
         </is>
       </c>
-      <c r="B598" s="4" t="inlineStr">
+      <c r="B598" t="inlineStr">
         <is>
           <t>ebr85755504</t>
         </is>
       </c>
-      <c r="C598" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D598" s="4" t="inlineStr"/>
-      <c r="E598" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F598" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>LG Washer Display Board Assembly - EBR85755504</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>lgparts.com display PCB (washer-dryer-combo collection); newegg control board for WT7250CW/WT7300CV, alt EBR86692701</t>
         </is>
       </c>
     </row>
     <row r="599">
-      <c r="A599" s="4" t="inlineStr">
+      <c r="A599" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/mkk63022401</t>
         </is>
       </c>
-      <c r="B599" s="4" t="inlineStr">
+      <c r="B599" s="3" t="inlineStr">
         <is>
           <t>mkk63022401</t>
         </is>
       </c>
-      <c r="C599" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D599" s="4" t="inlineStr"/>
-      <c r="E599" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F599" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C599" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D599" s="3" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Ice Bucket - MKK63022401</t>
+        </is>
+      </c>
+      <c r="E599" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F599" s="3" t="inlineStr">
+        <is>
+          <t>exact number not found; MKK-series siblings MKK63362302/MKK62542401/MKK61841801 are refrigerator ice buckets (ifixit.com, lgparts.com)</t>
         </is>
       </c>
     </row>
@@ -18969,114 +19643,130 @@
       </c>
     </row>
     <row r="601">
-      <c r="A601" s="4" t="inlineStr">
+      <c r="A601" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/akc73249303</t>
         </is>
       </c>
-      <c r="B601" s="4" t="inlineStr">
+      <c r="B601" t="inlineStr">
         <is>
           <t>akc73249303</t>
         </is>
       </c>
-      <c r="C601" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D601" s="4" t="inlineStr"/>
-      <c r="E601" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F601" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Ice Bucket Assembly - AKC73249303</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>lgparts.com, filtersfast.com; superseded by AKC73249305 (previous AKC73249304)</t>
         </is>
       </c>
     </row>
     <row r="602">
-      <c r="A602" s="4" t="inlineStr">
+      <c r="A602" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/aed37082970</t>
         </is>
       </c>
-      <c r="B602" s="4" t="inlineStr">
+      <c r="B602" t="inlineStr">
         <is>
           <t>aed37082970</t>
         </is>
       </c>
-      <c r="C602" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D602" s="4" t="inlineStr"/>
-      <c r="E602" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F602" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Door Handle Assembly - AED37082970</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>lgparts.com, filtersfast.com (LFX31945ST, LFXC24796S)</t>
         </is>
       </c>
     </row>
     <row r="603">
-      <c r="A603" s="4" t="inlineStr">
+      <c r="A603" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/adx73670402</t>
         </is>
       </c>
-      <c r="B603" s="4" t="inlineStr">
+      <c r="B603" s="3" t="inlineStr">
         <is>
           <t>adx73670402</t>
         </is>
       </c>
-      <c r="C603" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D603" s="4" t="inlineStr"/>
-      <c r="E603" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F603" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C603" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D603" s="3" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Door Gasket Assembly - ADX73670402</t>
+        </is>
+      </c>
+      <c r="E603" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F603" s="3" t="inlineStr">
+        <is>
+          <t>exact number not found; siblings ADX73670401 (refrigerator door gasket, lgparts.com), ADX73670408 (freezer lower door gasket, newegg.com)</t>
         </is>
       </c>
     </row>
     <row r="604">
-      <c r="A604" s="4" t="inlineStr">
+      <c r="A604" s="2" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/aaa75232311</t>
         </is>
       </c>
-      <c r="B604" s="4" t="inlineStr">
+      <c r="B604" s="2" t="inlineStr">
         <is>
           <t>aaa75232311</t>
         </is>
       </c>
-      <c r="C604" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D604" s="4" t="inlineStr"/>
-      <c r="E604" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F604" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C604" s="2" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D604" s="2" t="inlineStr">
+        <is>
+          <t>LG Dryer Steam Hose Installation Kit - AAA75232311</t>
+        </is>
+      </c>
+      <c r="E604" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F604" s="2" t="inlineStr">
+        <is>
+          <t>lgparts.com (steam hose kit, washer-dryer combo collection); sibling AAA75232303 dryer hose installation kit; appliance inferred</t>
         </is>
       </c>
     </row>
@@ -19113,30 +19803,34 @@
       </c>
     </row>
     <row r="606">
-      <c r="A606" s="4" t="inlineStr">
+      <c r="A606" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/adx73350628</t>
         </is>
       </c>
-      <c r="B606" s="4" t="inlineStr">
+      <c r="B606" t="inlineStr">
         <is>
           <t>adx73350628</t>
         </is>
       </c>
-      <c r="C606" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D606" s="4" t="inlineStr"/>
-      <c r="E606" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F606" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Door Gasket - ADX73350628</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>lgparts.com refrigerator-parts (fr)</t>
         </is>
       </c>
     </row>
@@ -19269,30 +19963,34 @@
       </c>
     </row>
     <row r="611">
-      <c r="A611" s="4" t="inlineStr">
+      <c r="A611" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/agl73852522</t>
         </is>
       </c>
-      <c r="B611" s="4" t="inlineStr">
+      <c r="B611" t="inlineStr">
         <is>
           <t>agl73852522</t>
         </is>
       </c>
-      <c r="C611" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D611" s="4" t="inlineStr"/>
-      <c r="E611" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F611" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>LG Washer Dispenser Drawer Panel - AGL73852522</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>lgparts.com washer drawer panel (detergent and softener sections)</t>
         </is>
       </c>
     </row>
@@ -19361,86 +20059,98 @@
       </c>
     </row>
     <row r="614">
-      <c r="A614" s="4" t="inlineStr">
+      <c r="A614" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/mjh66253301</t>
         </is>
       </c>
-      <c r="B614" s="4" t="inlineStr">
+      <c r="B614" s="3" t="inlineStr">
         <is>
           <t>mjh66253301</t>
         </is>
       </c>
-      <c r="C614" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D614" s="4" t="inlineStr"/>
-      <c r="E614" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F614" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C614" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D614" s="3" t="inlineStr">
+        <is>
+          <t>LG Range Support Bracket - MJH66253301</t>
+        </is>
+      </c>
+      <c r="E614" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F614" s="3" t="inlineStr">
+        <is>
+          <t>exact number not found; MJH prefix is LG supporter/bracket family; nearby MJH66251901 range support bracket on lgparts.com</t>
         </is>
       </c>
     </row>
     <row r="615">
-      <c r="A615" s="4" t="inlineStr">
+      <c r="A615" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/adq74813411</t>
         </is>
       </c>
-      <c r="B615" s="4" t="inlineStr">
+      <c r="B615" t="inlineStr">
         <is>
           <t>adq74813411</t>
         </is>
       </c>
-      <c r="C615" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D615" s="4" t="inlineStr"/>
-      <c r="E615" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F615" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Water Filter - ADQ74813411</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>lgparts.com</t>
         </is>
       </c>
     </row>
     <row r="616">
-      <c r="A616" s="4" t="inlineStr">
+      <c r="A616" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/adc74129518</t>
         </is>
       </c>
-      <c r="B616" s="4" t="inlineStr">
+      <c r="B616" t="inlineStr">
         <is>
           <t>adc74129518</t>
         </is>
       </c>
-      <c r="C616" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D616" s="4" t="inlineStr"/>
-      <c r="E616" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F616" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>LG Dryer Door Assembly - ADC74129518</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>lgparts.com LG ADC74129518 Dryer Door Assembly</t>
         </is>
       </c>
     </row>
@@ -19573,114 +20283,130 @@
       </c>
     </row>
     <row r="621">
-      <c r="A621" s="4" t="inlineStr">
+      <c r="A621" s="2" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/6500jb1008d</t>
         </is>
       </c>
-      <c r="B621" s="4" t="inlineStr">
+      <c r="B621" s="2" t="inlineStr">
         <is>
           <t>6500jb1008d</t>
         </is>
       </c>
-      <c r="C621" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D621" s="4" t="inlineStr"/>
-      <c r="E621" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F621" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C621" s="2" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D621" s="2" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Temperature Sensor - 6500JB1008D</t>
+        </is>
+      </c>
+      <c r="E621" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F621" s="2" t="inlineStr">
+        <is>
+          <t>only a reseller listing names exact number as refrigerator temperature sensor; siblings 6500JB1008A/F (ifixit.com, boulanger.com)</t>
         </is>
       </c>
     </row>
     <row r="622">
-      <c r="A622" s="4" t="inlineStr">
+      <c r="A622" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/3551dd2001j</t>
         </is>
       </c>
-      <c r="B622" s="4" t="inlineStr">
+      <c r="B622" t="inlineStr">
         <is>
           <t>3551dd2001j</t>
         </is>
       </c>
-      <c r="C622" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D622" s="4" t="inlineStr"/>
-      <c r="E622" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F622" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>LG Dishwasher Lower Cover Assembly - 3551DD2001J</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>lgparts.com</t>
         </is>
       </c>
     </row>
     <row r="623">
-      <c r="A623" s="4" t="inlineStr">
+      <c r="A623" s="2" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/cls30760101</t>
         </is>
       </c>
-      <c r="B623" s="4" t="inlineStr">
+      <c r="B623" s="2" t="inlineStr">
         <is>
           <t>cls30760101</t>
         </is>
       </c>
-      <c r="C623" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D623" s="4" t="inlineStr"/>
-      <c r="E623" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F623" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C623" s="2" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D623" s="2" t="inlineStr">
+        <is>
+          <t>LG Warm Dark Gray Touch Up Paint - CLS30760101</t>
+        </is>
+      </c>
+      <c r="E623" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F623" s="2" t="inlineStr">
+        <is>
+          <t>Appliance not identified. lgparts.com touch up paint, warm dark gray with brush; appliance not stated</t>
         </is>
       </c>
     </row>
     <row r="624">
-      <c r="A624" s="4" t="inlineStr">
+      <c r="A624" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/aht74574205</t>
         </is>
       </c>
-      <c r="B624" s="4" t="inlineStr">
+      <c r="B624" t="inlineStr">
         <is>
           <t>aht74574205</t>
         </is>
       </c>
-      <c r="C624" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D624" s="4" t="inlineStr"/>
-      <c r="E624" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F624" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Shelf Assembly - AHT74574205</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>lgparts.com, partswarehouse.com, newegg.com; supersedes AHT74574201/AHT74574203/MHL64031501</t>
         </is>
       </c>
     </row>
@@ -19717,30 +20443,34 @@
       </c>
     </row>
     <row r="626">
-      <c r="A626" s="4" t="inlineStr">
+      <c r="A626" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/ebz63405072</t>
         </is>
       </c>
-      <c r="B626" s="4" t="inlineStr">
+      <c r="B626" s="3" t="inlineStr">
         <is>
           <t>ebz63405072</t>
         </is>
       </c>
-      <c r="C626" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D626" s="4" t="inlineStr"/>
-      <c r="E626" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F626" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C626" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D626" s="3" t="inlineStr">
+        <is>
+          <t>LG Range Hood Control Panel Assembly - EBZ63405072</t>
+        </is>
+      </c>
+      <c r="E626" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F626" s="3" t="inlineStr">
+        <is>
+          <t>lgparts.com lists exact number with no description; siblings EBZ63405071 control panel, EBZ63405051 range hood main PCB</t>
         </is>
       </c>
     </row>
@@ -19809,58 +20539,66 @@
       </c>
     </row>
     <row r="629">
-      <c r="A629" s="4" t="inlineStr">
+      <c r="A629" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/5214a20027b</t>
         </is>
       </c>
-      <c r="B629" s="4" t="inlineStr">
+      <c r="B629" s="3" t="inlineStr">
         <is>
           <t>5214a20027b</t>
         </is>
       </c>
-      <c r="C629" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D629" s="4" t="inlineStr"/>
-      <c r="E629" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F629" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C629" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D629" s="3" t="inlineStr">
+        <is>
+          <t>LG Air Conditioner Pipe Assembly - 5214A20027B</t>
+        </is>
+      </c>
+      <c r="E629" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F629" s="3" t="inlineStr">
+        <is>
+          <t>no source found for exact number; 52xxA200xx numbering is LG air conditioner parts; name guessed</t>
         </is>
       </c>
     </row>
     <row r="630">
-      <c r="A630" s="4" t="inlineStr">
+      <c r="A630" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/4987jj2002r</t>
         </is>
       </c>
-      <c r="B630" s="4" t="inlineStr">
+      <c r="B630" t="inlineStr">
         <is>
           <t>4987jj2002r</t>
         </is>
       </c>
-      <c r="C630" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D630" s="4" t="inlineStr"/>
-      <c r="E630" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F630" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>LG Refrigerator Door Gasket - 4987JJ2002R</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>lgparts.com, appliancefactoryparts.com (unavailable; alt 4987JJ2002D)</t>
         </is>
       </c>
     </row>
@@ -19897,58 +20635,66 @@
       </c>
     </row>
     <row r="632">
-      <c r="A632" s="4" t="inlineStr">
+      <c r="A632" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/mcr67468501</t>
         </is>
       </c>
-      <c r="B632" s="4" t="inlineStr">
+      <c r="B632" t="inlineStr">
         <is>
           <t>mcr67468501</t>
         </is>
       </c>
-      <c r="C632" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D632" s="4" t="inlineStr"/>
-      <c r="E632" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F632" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>LG Range Backguard Trim - MCR67468501</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>lgparts.com range collection (rear decor trim)</t>
         </is>
       </c>
     </row>
     <row r="633">
-      <c r="A633" s="4" t="inlineStr">
+      <c r="A633" s="2" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/agb74272405</t>
         </is>
       </c>
-      <c r="B633" s="4" t="inlineStr">
+      <c r="B633" s="2" t="inlineStr">
         <is>
           <t>agb74272405</t>
         </is>
       </c>
-      <c r="C633" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D633" s="4" t="inlineStr"/>
-      <c r="E633" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F633" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C633" s="2" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D633" s="2" t="inlineStr">
+        <is>
+          <t>LG Vacuum Turbine Nozzle Assembly - AGB74272405</t>
+        </is>
+      </c>
+      <c r="E633" s="2" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="F633" s="2" t="inlineStr">
+        <is>
+          <t>lgparts.com, partswarehouse.com Nozzle Assembly, Turbine; appliance inferred (cordless stick vacuum)</t>
         </is>
       </c>
     </row>
@@ -20145,30 +20891,34 @@
       </c>
     </row>
     <row r="640">
-      <c r="A640" s="4" t="inlineStr">
+      <c r="A640" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/ebr76542917</t>
         </is>
       </c>
-      <c r="B640" s="4" t="inlineStr">
+      <c r="B640" t="inlineStr">
         <is>
           <t>ebr76542917</t>
         </is>
       </c>
-      <c r="C640" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D640" s="4" t="inlineStr"/>
-      <c r="E640" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F640" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>LG Dryer Main Control Board - EBR76542917</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>lgparts.com (dryer collection), ifixit.com</t>
         </is>
       </c>
     </row>
@@ -20237,30 +20987,34 @@
       </c>
     </row>
     <row r="643">
-      <c r="A643" s="4" t="inlineStr">
+      <c r="A643" s="3" t="inlineStr">
         <is>
           <t>https://lgparts.com/products/ebr39528804</t>
         </is>
       </c>
-      <c r="B643" s="4" t="inlineStr">
+      <c r="B643" s="3" t="inlineStr">
         <is>
           <t>ebr39528804</t>
         </is>
       </c>
-      <c r="C643" s="4" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="D643" s="4" t="inlineStr"/>
-      <c r="E643" s="4" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="F643" s="4" t="inlineStr">
-        <is>
-          <t>Not researched yet - next search round</t>
+      <c r="C643" s="3" t="inlineStr">
+        <is>
+          <t>LG</t>
+        </is>
+      </c>
+      <c r="D643" s="3" t="inlineStr">
+        <is>
+          <t>LG Dryer Main Control Board - EBR39528804</t>
+        </is>
+      </c>
+      <c r="E643" s="3" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="F643" s="3" t="inlineStr">
+        <is>
+          <t>exact not found; siblings EBR39528805/06 dryer control board (shopjimmy, mercadolibre)</t>
         </is>
       </c>
     </row>
